--- a/error_models/conv_models/nv_8x16_b1_dat-2097152_wt-262144_int32/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_8x16_b1_dat-2097152_wt-262144_int32/unique_complete_df.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T40"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -529,6 +529,136 @@
           <t>Skip4</t>
         </is>
       </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-single</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>bullet_wake-multi</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-single</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_alternated_blocks-multi</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-single</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>single_channel_random-multi</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>single-single</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>single-multi</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-single</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>multiple_channels_uncategorized-multi</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-single</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>single_block-multi</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-single</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>quasi_shattered_channel-multi</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-single</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>skip_4-multi</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-single</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>same_row-multi</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-single</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>multi_channel_block-multi</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-single</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>rectangles-multi</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-single</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>full_channels-multi</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
@@ -552,13 +682,13 @@
         <v>2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9991791415641268</v>
+        <v>0.9991975471150696</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0008185395414389</v>
+        <v>0.0008005614541229</v>
       </c>
       <c r="I2" t="n">
-        <v>2.305832889967136e-06</v>
+        <v>1.878369262987541e-06</v>
       </c>
       <c r="J2" t="n">
         <v>0.0878434595002888</v>
@@ -582,7 +712,7 @@
         <v>2.366511540007909e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>3.213534493679229e-05</v>
+        <v>3.21353449367923e-05</v>
       </c>
       <c r="R2" t="n">
         <v>8.127366864892824e-07</v>
@@ -592,6 +722,84 @@
       </c>
       <c r="T2" t="n">
         <v>4.062506508837567e-07</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.1113504248635288</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.8886495751364712</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -616,19 +824,19 @@
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9986465837801308</v>
+        <v>0.9986701951756304</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0013510170501083</v>
+        <v>0.0013277994797013</v>
       </c>
       <c r="I3" t="n">
-        <v>2.386108216688113e-06</v>
+        <v>1.992283123832815e-06</v>
       </c>
       <c r="J3" t="n">
         <v>0.0506987974226653</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8403391379221127</v>
+        <v>0.8403391379221128</v>
       </c>
       <c r="L3" t="n">
         <v>0.089076374012618</v>
@@ -656,6 +864,84 @@
       </c>
       <c r="T3" t="n">
         <v>1.82515289528598e-07</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0</v>
+      </c>
+      <c r="V3" t="n">
+        <v>1</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.1113444759371124</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.8886555240628875</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -680,13 +966,13 @@
         <v>1</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9995694709478316</v>
+        <v>0.999573400330842</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0004279252402232</v>
+        <v>0.0004243097048239</v>
       </c>
       <c r="I4" t="n">
-        <v>2.59075040066586e-06</v>
+        <v>2.276902789690739e-06</v>
       </c>
       <c r="J4" t="n">
         <v>0.0003301062947583</v>
@@ -720,6 +1006,84 @@
       </c>
       <c r="T4" t="n">
         <v>1.335351546184232e-06</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>1</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.6574653291876419</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.3425346708123581</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.1113244558408738</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.8886755441591262</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -744,19 +1108,19 @@
         <v>1</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9990570429659372</v>
+        <v>0.9990612380563292</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0009404419800015</v>
+        <v>0.0009365656434828</v>
       </c>
       <c r="I5" t="n">
-        <v>2.501992516677656e-06</v>
+        <v>2.18323864357897e-06</v>
       </c>
       <c r="J5" t="n">
         <v>0.0064923047449558</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8814956825172965</v>
+        <v>0.8814956825172966</v>
       </c>
       <c r="L5" t="n">
         <v>0.035572753840585</v>
@@ -784,6 +1148,84 @@
       </c>
       <c r="T5" t="n">
         <v>0.0003530470999054</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>1</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>0.9949826361973588</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0.0050173638026413</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.1113432147229741</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.8886567852770257</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -808,13 +1250,13 @@
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9994677119307548</v>
+        <v>0.9994716259303384</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0005297309642749</v>
+        <v>0.0005261298892054</v>
       </c>
       <c r="I6" t="n">
-        <v>2.544043425859468e-06</v>
+        <v>2.231118911880177e-06</v>
       </c>
       <c r="J6" t="n">
         <v>0.004620684769454</v>
@@ -848,6 +1290,84 @@
       </c>
       <c r="T6" t="n">
         <v>0.0006239376566055</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>0.9934131969296984</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0.0065868030703015</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.111029911509987</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.888970088490013</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -872,19 +1392,19 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>0.9992083059246364</v>
+        <v>0.9994082408130508</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0007893218229921</v>
+        <v>0.0005897996863628</v>
       </c>
       <c r="I7" t="n">
-        <v>2.359190827201905e-06</v>
+        <v>1.946439042070148e-06</v>
       </c>
       <c r="J7" t="n">
         <v>0.1753294923476672</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7351684291541375</v>
+        <v>0.7351684291541376</v>
       </c>
       <c r="L7" t="n">
         <v>0.021917101589674</v>
@@ -912,6 +1432,84 @@
       </c>
       <c r="T7" t="n">
         <v>2.032609289285583e-07</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>1</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.1115502018549213</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.8884497981450786</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -936,19 +1534,19 @@
         <v>1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.9992370763302598</v>
+        <v>0.9992838816750572</v>
       </c>
       <c r="H8" t="n">
-        <v>0.000760460907581</v>
+        <v>0.0007140496039309</v>
       </c>
       <c r="I8" t="n">
-        <v>2.449700614670064e-06</v>
+        <v>2.05565946756158e-06</v>
       </c>
       <c r="J8" t="n">
         <v>0.0441470046152142</v>
       </c>
       <c r="K8" t="n">
-        <v>0.8496980824933246</v>
+        <v>0.8496980824933247</v>
       </c>
       <c r="L8" t="n">
         <v>0.0634366739301359</v>
@@ -976,6 +1574,84 @@
       </c>
       <c r="T8" t="n">
         <v>0.0060661304312059</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.1110645068045804</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.8889354931954195</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -1000,13 +1676,13 @@
         <v>0</v>
       </c>
       <c r="G9" t="n">
-        <v>0.9992923607250982</v>
+        <v>0.9995612056103144</v>
       </c>
       <c r="H9" t="n">
-        <v>0.000704933463243</v>
+        <v>0.0004363789024224</v>
       </c>
       <c r="I9" t="n">
-        <v>2.692750114387718e-06</v>
+        <v>2.402425718856577e-06</v>
       </c>
       <c r="J9" t="n">
         <v>0.0918955732408166</v>
@@ -1040,6 +1716,84 @@
       </c>
       <c r="T9" t="n">
         <v>1.182149714695386e-06</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>1</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -1064,13 +1818,13 @@
         <v>0</v>
       </c>
       <c r="G10" t="n">
-        <v>0.9997868795764592</v>
+        <v>0.999793350780705</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0002105913111404</v>
+        <v>0.0002043711655386</v>
       </c>
       <c r="I10" t="n">
-        <v>2.516050856236048e-06</v>
+        <v>2.264992211973501e-06</v>
       </c>
       <c r="J10" t="n">
         <v>0.0021206176578535</v>
@@ -1104,6 +1858,84 @@
       </c>
       <c r="T10" t="n">
         <v>0</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" t="n">
+        <v>1</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1128,13 +1960,13 @@
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9999461529942828</v>
+        <v>0.999953263176279</v>
       </c>
       <c r="H11" t="n">
-        <v>5.133730142846442e-05</v>
+        <v>4.450274029329908e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>2.49664274430598e-06</v>
+        <v>2.221021883335285e-06</v>
       </c>
       <c r="J11" t="n">
         <v>1.864912969121469e-05</v>
@@ -1168,6 +2000,84 @@
       </c>
       <c r="T11" t="n">
         <v>0</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" t="n">
+        <v>1</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1192,13 +2102,13 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9995396329823936</v>
+        <v>0.9995801245650228</v>
       </c>
       <c r="H12" t="n">
-        <v>0.0004578033087045</v>
+        <v>0.0004175766292134</v>
       </c>
       <c r="I12" t="n">
-        <v>2.550647357321941e-06</v>
+        <v>2.285744219596903e-06</v>
       </c>
       <c r="J12" t="n">
         <v>7.426037804591282e-05</v>
@@ -1219,7 +2129,7 @@
         <v>2.904968200239127e-09</v>
       </c>
       <c r="P12" t="n">
-        <v>0.8860743740075361</v>
+        <v>0.886074374007536</v>
       </c>
       <c r="Q12" t="n">
         <v>0.103150750309685</v>
@@ -1232,6 +2142,84 @@
       </c>
       <c r="T12" t="n">
         <v>1.526770857003524e-06</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" t="n">
+        <v>1</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
@@ -1256,13 +2244,13 @@
         <v>0</v>
       </c>
       <c r="G13" t="n">
-        <v>0.999907529236812</v>
+        <v>0.9999349133295612</v>
       </c>
       <c r="H13" t="n">
-        <v>8.981596445006352e-05</v>
+        <v>6.275045621555766e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>2.641737193369594e-06</v>
+        <v>2.32315267899147e-06</v>
       </c>
       <c r="J13" t="n">
         <v>0.0122477330479631</v>
@@ -1292,10 +2280,88 @@
         <v>4.983399388942951e-06</v>
       </c>
       <c r="S13" t="n">
-        <v>3.647900972583919e-05</v>
+        <v>3.64790097258392e-05</v>
       </c>
       <c r="T13" t="n">
         <v>1.003429903848309e-06</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1320,13 +2386,13 @@
         <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0.9994502594251758</v>
+        <v>0.9995234281031916</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0005471298937453</v>
+        <v>0.0004742154134557</v>
       </c>
       <c r="I14" t="n">
-        <v>2.597619534519408e-06</v>
+        <v>2.34342180840744e-06</v>
       </c>
       <c r="J14" t="n">
         <v>0.0540312689791262</v>
@@ -1360,6 +2426,84 @@
       </c>
       <c r="T14" t="n">
         <v>5.483435466754749e-07</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>1</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1384,13 +2528,13 @@
         <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>0.999894094793064</v>
+        <v>0.999924587250918</v>
       </c>
       <c r="H15" t="n">
-        <v>0.0001032181972121</v>
+        <v>7.304631242335402e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>2.673948179351536e-06</v>
+        <v>2.353375114201529e-06</v>
       </c>
       <c r="J15" t="n">
         <v>7.119143629388023e-05</v>
@@ -1424,6 +2568,84 @@
       </c>
       <c r="T15" t="n">
         <v>9.735058511936805e-07</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1448,13 +2670,13 @@
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9999363178421132</v>
+        <v>0.9999521494606316</v>
       </c>
       <c r="H16" t="n">
-        <v>6.109961830892827e-05</v>
+        <v>4.559166776333455e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>2.569478033503954e-06</v>
+        <v>2.24581006064638e-06</v>
       </c>
       <c r="J16" t="n">
         <v>3.917360580208432e-05</v>
@@ -1488,6 +2710,84 @@
       </c>
       <c r="T16" t="n">
         <v>1.01351692184967e-06</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" t="n">
+        <v>1</v>
+      </c>
+      <c r="W16" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1512,13 +2812,13 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9997995118496013</v>
+        <v>0.999811105723736</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0001979189349547</v>
+        <v>0.0001865735473452</v>
       </c>
       <c r="I17" t="n">
-        <v>2.556153899579967e-06</v>
+        <v>2.307667374242729e-06</v>
       </c>
       <c r="J17" t="n">
         <v>0.0007374773990412</v>
@@ -1533,7 +2833,7 @@
         <v>0.006509296197014</v>
       </c>
       <c r="N17" t="n">
-        <v>6.598229036821053e-06</v>
+        <v>6.598229036821054e-06</v>
       </c>
       <c r="O17" t="n">
         <v>8.982674899592562e-07</v>
@@ -1552,6 +2852,84 @@
       </c>
       <c r="T17" t="n">
         <v>0.0014449286935125</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1576,19 +2954,19 @@
         <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>0.9999697678458278</v>
+        <v>0.9999795799179512</v>
       </c>
       <c r="H18" t="n">
-        <v>2.767616357463348e-05</v>
+        <v>1.81856185804048e-05</v>
       </c>
       <c r="I18" t="n">
-        <v>2.542929053250668e-06</v>
+        <v>2.221401924245514e-06</v>
       </c>
       <c r="J18" t="n">
         <v>4.337866645963501e-05</v>
       </c>
       <c r="K18" t="n">
-        <v>5.317699777832805e-06</v>
+        <v>5.317699777832803e-06</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -1603,7 +2981,7 @@
         <v>5.965777920310406e-11</v>
       </c>
       <c r="P18" t="n">
-        <v>0.9953215116392706</v>
+        <v>0.9953215116392704</v>
       </c>
       <c r="Q18" t="n">
         <v>1.130272343224036e-05</v>
@@ -1616,6 +2994,84 @@
       </c>
       <c r="T18" t="n">
         <v>1.881446773749673e-06</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" t="n">
+        <v>1</v>
+      </c>
+      <c r="W18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1640,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="G19" t="n">
-        <v>0.9998458275489804</v>
+        <v>0.9998542138158882</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0001515902889958</v>
+        <v>0.0001434648749357</v>
       </c>
       <c r="I19" t="n">
-        <v>2.569100479360996e-06</v>
+        <v>2.308247631640014e-06</v>
       </c>
       <c r="J19" t="n">
-        <v>2.375125604286223e-05</v>
+        <v>2.375125604286222e-05</v>
       </c>
       <c r="K19" t="n">
         <v>0.9631550444220917</v>
@@ -1680,6 +3136,84 @@
       </c>
       <c r="T19" t="n">
         <v>0</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>1</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1704,19 +3238,19 @@
         <v>0</v>
       </c>
       <c r="G20" t="n">
-        <v>0.9999162111831658</v>
+        <v>0.9999272398061402</v>
       </c>
       <c r="H20" t="n">
-        <v>8.131592995333995e-05</v>
+        <v>7.058027941112731e-05</v>
       </c>
       <c r="I20" t="n">
-        <v>2.459825336496802e-06</v>
+        <v>2.166852904335762e-06</v>
       </c>
       <c r="J20" t="n">
         <v>0.0015343937649566</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9847414716930336</v>
+        <v>0.9847414716930338</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -1725,7 +3259,7 @@
         <v>2.358807812194662e-06</v>
       </c>
       <c r="N20" t="n">
-        <v>3.224978206909061e-06</v>
+        <v>3.22497820690906e-06</v>
       </c>
       <c r="O20" t="n">
         <v>7.831276487546329e-09</v>
@@ -1744,6 +3278,84 @@
       </c>
       <c r="T20" t="n">
         <v>0</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1768,13 +3380,13 @@
         <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>0.9997894979092146</v>
+        <v>0.9997959884323204</v>
       </c>
       <c r="H21" t="n">
-        <v>0.000208056995286</v>
+        <v>0.0002018128999933</v>
       </c>
       <c r="I21" t="n">
-        <v>2.432033954894196e-06</v>
+        <v>2.185606141702294e-06</v>
       </c>
       <c r="J21" t="n">
         <v>0.0044361887073789</v>
@@ -1808,6 +3420,84 @@
       </c>
       <c r="T21" t="n">
         <v>0</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" t="n">
+        <v>1</v>
+      </c>
+      <c r="W21" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1832,19 +3522,19 @@
         <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0982611697437652</v>
+        <v>0.6876122490635312</v>
       </c>
       <c r="H22" t="n">
-        <v>0.9017363898964924</v>
+        <v>0.3123855519867539</v>
       </c>
       <c r="I22" t="n">
-        <v>2.427298197910722e-06</v>
+        <v>2.185888170510363e-06</v>
       </c>
       <c r="J22" t="n">
         <v>0.0001214651094429</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9985773268196144</v>
+        <v>0.9985773268196142</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -1872,6 +3562,84 @@
       </c>
       <c r="T22" t="n">
         <v>0</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" t="n">
+        <v>1</v>
+      </c>
+      <c r="W22" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1896,13 +3664,13 @@
         <v>0</v>
       </c>
       <c r="G23" t="n">
-        <v>0.0991978499101535</v>
+        <v>0.6895415817693646</v>
       </c>
       <c r="H23" t="n">
-        <v>0.9007995798031416</v>
+        <v>0.3104560890518303</v>
       </c>
       <c r="I23" t="n">
-        <v>2.557225160470022e-06</v>
+        <v>2.31611726058967e-06</v>
       </c>
       <c r="J23" t="n">
         <v>2.429430033434606e-05</v>
@@ -1917,13 +3685,13 @@
         <v>6.17894669652062e-06</v>
       </c>
       <c r="N23" t="n">
-        <v>3.451323108963336e-07</v>
+        <v>3.451323108963335e-07</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.006719284732822e-07</v>
+        <v>1.006719284732821e-07</v>
       </c>
       <c r="Q23" t="n">
         <v>0.0005588745522713</v>
@@ -1936,6 +3704,84 @@
       </c>
       <c r="T23" t="n">
         <v>1.874059911383807e-08</v>
+      </c>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1</v>
+      </c>
+      <c r="W23" t="n">
+        <v>0</v>
+      </c>
+      <c r="X23" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1960,13 +3806,13 @@
         <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>0.99919180416571</v>
+        <v>0.9992207359226744</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0008054934362955</v>
+        <v>0.0007768036068771</v>
       </c>
       <c r="I24" t="n">
-        <v>2.689336450112457e-06</v>
+        <v>2.447408904054284e-06</v>
       </c>
       <c r="J24" t="n">
         <v>0.0048509614599044</v>
@@ -2000,6 +3846,84 @@
       </c>
       <c r="T24" t="n">
         <v>1.723088346270953e-06</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
+      </c>
+      <c r="V24" t="n">
+        <v>1</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -2024,13 +3948,13 @@
         <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>0.9995810759876002</v>
+        <v>0.9995911557656204</v>
       </c>
       <c r="H25" t="n">
-        <v>0.0004163568323516</v>
+        <v>0.0004065229396586</v>
       </c>
       <c r="I25" t="n">
-        <v>2.554118503888863e-06</v>
+        <v>2.308233176546458e-06</v>
       </c>
       <c r="J25" t="n">
         <v>0.001252052380788</v>
@@ -2051,7 +3975,7 @@
         <v>2.6719809029612e-09</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9019072862842396</v>
+        <v>0.9019072862842394</v>
       </c>
       <c r="Q25" t="n">
         <v>0.08431022925665239</v>
@@ -2064,6 +3988,84 @@
       </c>
       <c r="T25" t="n">
         <v>0.0007389242496067</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
+      </c>
+      <c r="V25" t="n">
+        <v>1</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ25" t="n">
+        <v>1</v>
+      </c>
+      <c r="AR25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -2088,13 +4090,13 @@
         <v>1</v>
       </c>
       <c r="G26" t="n">
-        <v>0.9996653588451349</v>
+        <v>0.9996680678072124</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0003334371268647</v>
+        <v>0.0003310160111192</v>
       </c>
       <c r="I26" t="n">
-        <v>1.190966456024169e-06</v>
+        <v>9.031201238278807e-07</v>
       </c>
       <c r="J26" t="n">
         <v>0.0018506265163714</v>
@@ -2128,6 +4130,84 @@
       </c>
       <c r="T26" t="n">
         <v>0.0028998089264526</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0.9986721877849712</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0.0013278122150287</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0.1112288009541753</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0.8887711990458247</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -2152,13 +4232,13 @@
         <v>1</v>
       </c>
       <c r="G27" t="n">
-        <v>0.9988420061428877</v>
+        <v>0.99888207517877</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0011556033070823</v>
+        <v>0.0011159215890448</v>
       </c>
       <c r="I27" t="n">
-        <v>2.37748848577033e-06</v>
+        <v>1.990170640839141e-06</v>
       </c>
       <c r="J27" t="n">
         <v>0.0477676752063472</v>
@@ -2173,13 +4253,13 @@
         <v>0.0105882876871841</v>
       </c>
       <c r="N27" t="n">
-        <v>0.0264541280089211</v>
+        <v>0.026454128008921</v>
       </c>
       <c r="O27" t="n">
         <v>0.0113348182092279</v>
       </c>
       <c r="P27" t="n">
-        <v>2.836818900331345e-06</v>
+        <v>2.836818900331346e-06</v>
       </c>
       <c r="Q27" t="n">
         <v>0.011390273669404</v>
@@ -2191,7 +4271,85 @@
         <v>3.732367462237458e-06</v>
       </c>
       <c r="T27" t="n">
-        <v>8.94900256232544e-07</v>
+        <v>8.949002562325439e-07</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>1</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0.1111784692725899</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0.88882153072741</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2216,13 +4374,13 @@
         <v>1</v>
       </c>
       <c r="G28" t="n">
-        <v>0.9994177176625724</v>
+        <v>0.99942515141177</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0005798202167189</v>
+        <v>0.0005727496680335</v>
       </c>
       <c r="I28" t="n">
-        <v>2.449059164551751e-06</v>
+        <v>2.085858652156289e-06</v>
       </c>
       <c r="J28" t="n">
         <v>0.0002631834033581</v>
@@ -2243,7 +4401,7 @@
         <v>0.0273924128605446</v>
       </c>
       <c r="P28" t="n">
-        <v>0.8766614655759279</v>
+        <v>0.8766614655759281</v>
       </c>
       <c r="Q28" t="n">
         <v>0.009162509664844699</v>
@@ -2256,6 +4414,84 @@
       </c>
       <c r="T28" t="n">
         <v>0.0005189984122594</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>1</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0.6389108539205585</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0.3610891460794415</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -2280,13 +4516,13 @@
         <v>1</v>
       </c>
       <c r="G29" t="n">
-        <v>0.9988947318167194</v>
+        <v>0.9989024572327546</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0011028174244692</v>
+        <v>0.0010954443325015</v>
       </c>
       <c r="I29" t="n">
-        <v>2.437697267038572e-06</v>
+        <v>2.085373199513703e-06</v>
       </c>
       <c r="J29" t="n">
         <v>0.0003249499030717</v>
@@ -2307,7 +4543,7 @@
         <v>0.0208772974418185</v>
       </c>
       <c r="P29" t="n">
-        <v>0.8766516050471219</v>
+        <v>0.876651605047122</v>
       </c>
       <c r="Q29" t="n">
         <v>2.223139523310739e-05</v>
@@ -2320,6 +4556,84 @@
       </c>
       <c r="T29" t="n">
         <v>0.0010771625572955</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>1</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0.9985238453035939</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0.0014761546964058</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2344,13 +4658,13 @@
         <v>0</v>
       </c>
       <c r="G30" t="n">
-        <v>0.09776224941236319</v>
+        <v>0.687915780911081</v>
       </c>
       <c r="H30" t="n">
-        <v>0.9022351784047696</v>
+        <v>0.3120818685540765</v>
       </c>
       <c r="I30" t="n">
-        <v>2.559121322846147e-06</v>
+        <v>2.337473298073471e-06</v>
       </c>
       <c r="J30" t="n">
         <v>0.0004864291922182</v>
@@ -2365,7 +4679,7 @@
         <v>1.520115387407094e-05</v>
       </c>
       <c r="N30" t="n">
-        <v>6.577226033937299e-07</v>
+        <v>6.5772260339373e-07</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -2384,6 +4698,84 @@
       </c>
       <c r="T30" t="n">
         <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>1</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2408,13 +4800,13 @@
         <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>0.9984052766808784</v>
+        <v>0.998510113816204</v>
       </c>
       <c r="H31" t="n">
-        <v>0.0015922685920938</v>
+        <v>0.0014876800660199</v>
       </c>
       <c r="I31" t="n">
-        <v>2.441665483209356e-06</v>
+        <v>2.193056231599883e-06</v>
       </c>
       <c r="J31" t="n">
         <v>1.47890763001068e-06</v>
@@ -2429,7 +4821,7 @@
         <v>0.0027675886738829</v>
       </c>
       <c r="N31" t="n">
-        <v>3.618109221851632e-05</v>
+        <v>3.618109221851631e-05</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
@@ -2448,6 +4840,84 @@
       </c>
       <c r="T31" t="n">
         <v>0</v>
+      </c>
+      <c r="U31" t="n">
+        <v>0</v>
+      </c>
+      <c r="V31" t="n">
+        <v>1</v>
+      </c>
+      <c r="W31" t="n">
+        <v>0</v>
+      </c>
+      <c r="X31" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP31" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2472,19 +4942,19 @@
         <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>0.9959094608065538</v>
+        <v>0.9960449587225144</v>
       </c>
       <c r="H32" t="n">
-        <v>0.0040879423387729</v>
+        <v>0.0039526775500007</v>
       </c>
       <c r="I32" t="n">
-        <v>2.583793128867702e-06</v>
+        <v>2.350665940565848e-06</v>
       </c>
       <c r="J32" t="n">
         <v>5.946874348767533e-06</v>
       </c>
       <c r="K32" t="n">
-        <v>0.8811868742363758</v>
+        <v>0.8811868742363759</v>
       </c>
       <c r="L32" t="n">
         <v>1.34280672929432e-08</v>
@@ -2512,6 +4982,84 @@
       </c>
       <c r="T32" t="n">
         <v>0</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
+      </c>
+      <c r="V32" t="n">
+        <v>1</v>
+      </c>
+      <c r="W32" t="n">
+        <v>0</v>
+      </c>
+      <c r="X32" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2536,13 +5084,13 @@
         <v>2</v>
       </c>
       <c r="G33" t="n">
-        <v>0.9955010361986923</v>
+        <v>0.995515427360008</v>
       </c>
       <c r="H33" t="n">
-        <v>0.0044964943980201</v>
+        <v>0.0044825269896488</v>
       </c>
       <c r="I33" t="n">
-        <v>2.456341743018151e-06</v>
+        <v>2.032588798720574e-06</v>
       </c>
       <c r="J33" t="n">
         <v>9.588710215712296e-07</v>
@@ -2566,7 +5114,7 @@
         <v>6.682667512189507e-06</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.857281687835235e-05</v>
+        <v>3.857281687835234e-05</v>
       </c>
       <c r="R33" t="n">
         <v>2.556989390856627e-06</v>
@@ -2576,6 +5124,84 @@
       </c>
       <c r="T33" t="n">
         <v>0</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
+      </c>
+      <c r="V33" t="n">
+        <v>1</v>
+      </c>
+      <c r="W33" t="n">
+        <v>0</v>
+      </c>
+      <c r="X33" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ33" t="n">
+        <v>0.0006973143144272</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>0.9993026856855728</v>
+      </c>
+      <c r="AS33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2600,13 +5226,13 @@
         <v>2</v>
       </c>
       <c r="G34" t="n">
-        <v>0.2036881960419483</v>
+        <v>0.585715613474575</v>
       </c>
       <c r="H34" t="n">
-        <v>0.7963096113967465</v>
+        <v>0.4142826077704672</v>
       </c>
       <c r="I34" t="n">
-        <v>2.179499760665012e-06</v>
+        <v>1.765693413535188e-06</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2640,6 +5266,84 @@
       </c>
       <c r="T34" t="n">
         <v>0</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
+      </c>
+      <c r="V34" t="n">
+        <v>1</v>
+      </c>
+      <c r="W34" t="n">
+        <v>0</v>
+      </c>
+      <c r="X34" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP34" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2664,13 +5368,13 @@
         <v>1</v>
       </c>
       <c r="G35" t="n">
-        <v>0.9993387644592602</v>
+        <v>0.9994521224065214</v>
       </c>
       <c r="H35" t="n">
-        <v>0.00065879593153335</v>
+        <v>0.0005458481057323</v>
       </c>
       <c r="I35" t="n">
-        <v>2.426547662079825e-06</v>
+        <v>2.016426201907922e-06</v>
       </c>
       <c r="J35" t="n">
         <v>0.1449986133428514</v>
@@ -2704,6 +5408,84 @@
       </c>
       <c r="T35" t="n">
         <v>2.192191595980413e-07</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1</v>
+      </c>
+      <c r="W35" t="n">
+        <v>0</v>
+      </c>
+      <c r="X35" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0.1115481423019123</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0.8884518576980875</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2728,19 +5510,19 @@
         <v>1</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9957225868265018</v>
+        <v>0.9958791751886233</v>
       </c>
       <c r="H36" t="n">
-        <v>0.0042751541645627</v>
+        <v>0.0041189649497534</v>
       </c>
       <c r="I36" t="n">
-        <v>2.245947391011244e-06</v>
+        <v>1.8468000788543e-06</v>
       </c>
       <c r="J36" t="n">
         <v>0.0679886006995979</v>
       </c>
       <c r="K36" t="n">
-        <v>0.8179463845428169</v>
+        <v>0.817946384542817</v>
       </c>
       <c r="L36" t="n">
         <v>0.08478842279106345</v>
@@ -2768,6 +5550,84 @@
       </c>
       <c r="T36" t="n">
         <v>0.001826750180833314</v>
+      </c>
+      <c r="U36" t="n">
+        <v>0</v>
+      </c>
+      <c r="V36" t="n">
+        <v>1</v>
+      </c>
+      <c r="W36" t="n">
+        <v>0</v>
+      </c>
+      <c r="X36" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ36" t="n">
+        <v>4.045684717463313e-05</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>0.9999595431528253</v>
+      </c>
+      <c r="AS36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2792,13 +5652,13 @@
         <v>1</v>
       </c>
       <c r="G37" t="n">
-        <v>0.9974539537102324</v>
+        <v>0.9974987302026275</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0025438052649399</v>
+        <v>0.0024994083891999</v>
       </c>
       <c r="I37" t="n">
-        <v>2.227963283331167e-06</v>
+        <v>1.84834662819737e-06</v>
       </c>
       <c r="J37" t="n">
         <v>0.04885443782451615</v>
@@ -2832,6 +5692,84 @@
       </c>
       <c r="T37" t="n">
         <v>0.0001856175617355569</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
+      </c>
+      <c r="V37" t="n">
+        <v>1</v>
+      </c>
+      <c r="W37" t="n">
+        <v>0</v>
+      </c>
+      <c r="X37" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ37" t="n">
+        <v>7.593186896218585e-07</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>0.9999992406813103</v>
+      </c>
+      <c r="AS37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2856,13 +5794,13 @@
         <v>1</v>
       </c>
       <c r="G38" t="n">
-        <v>0.9979844312783911</v>
+        <v>0.9979990212574712</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0020131867390896</v>
+        <v>0.0019989391844899</v>
       </c>
       <c r="I38" t="n">
-        <v>2.368920974865074e-06</v>
+        <v>2.026496494465474e-06</v>
       </c>
       <c r="J38" t="n">
         <v>0.0003923447285396</v>
@@ -2896,6 +5834,84 @@
       </c>
       <c r="T38" t="n">
         <v>0.0001134465458266892</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1</v>
+      </c>
+      <c r="W38" t="n">
+        <v>0</v>
+      </c>
+      <c r="X38" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2920,13 +5936,13 @@
         <v>1</v>
       </c>
       <c r="G39" t="n">
-        <v>0.998458231118317</v>
+        <v>0.9984751852316146</v>
       </c>
       <c r="H39" t="n">
-        <v>0.0015393902804192</v>
+        <v>0.001522732027290325</v>
       </c>
       <c r="I39" t="n">
-        <v>2.36553971924604e-06</v>
+        <v>2.069679550679921e-06</v>
       </c>
       <c r="J39" t="n">
         <v>0.004106583082919475</v>
@@ -2960,6 +5976,84 @@
       </c>
       <c r="T39" t="n">
         <v>0.00169562883644655</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
+      </c>
+      <c r="V39" t="n">
+        <v>1</v>
+      </c>
+      <c r="W39" t="n">
+        <v>0</v>
+      </c>
+      <c r="X39" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>0.7497834260088212</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0.00021657399117865</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP39" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0.08335139364824007</v>
+      </c>
+      <c r="AR39" t="n">
+        <v>0.6666486063517598</v>
+      </c>
+      <c r="AS39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2984,13 +6078,13 @@
         <v>1</v>
       </c>
       <c r="G40" t="n">
-        <v>0.9995458502455039</v>
+        <v>0.99955099862434</v>
       </c>
       <c r="H40" t="n">
-        <v>0.0004516193520098</v>
+        <v>0.0004467542049895</v>
       </c>
       <c r="I40" t="n">
-        <v>2.517340941759131e-06</v>
+        <v>2.234109126211351e-06</v>
       </c>
       <c r="J40" t="n">
         <v>0.00742246114900285</v>
@@ -3024,6 +6118,84 @@
       </c>
       <c r="T40" t="n">
         <v>0.0016434088612988</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
+      </c>
+      <c r="V40" t="n">
+        <v>1</v>
+      </c>
+      <c r="W40" t="n">
+        <v>0</v>
+      </c>
+      <c r="X40" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>0.4985432088565234</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0.0014567911434765</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP40" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0.05560920051769665</v>
+      </c>
+      <c r="AR40" t="n">
+        <v>0.4443907994823033</v>
+      </c>
+      <c r="AS40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/error_models/conv_models/nv_8x16_b1_dat-2097152_wt-262144_int32/unique_complete_df.xlsx
+++ b/error_models/conv_models/nv_8x16_b1_dat-2097152_wt-262144_int32/unique_complete_df.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="unique_complete_layers" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,310 +425,315 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT40"/>
+  <dimension ref="A1:AV40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Unnamed: 0</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Layer</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Channels_in</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Channels_out</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Input_size</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Kernel_size</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Padding</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Masked</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>SDC</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Crash+Hang</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>FullChannels</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Rectangles</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>SingleChannelRandom</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>ShatteredChannel</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>QuasiShatteredChannel</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>MultiChannelBlock</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>BulletWake</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>SameRow</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>SingleBlock</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Skip4</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-single</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>shattered_channel-multi</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-single</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>bullet_wake-multi</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-single</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>single_channel_alternated_blocks-multi</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-single</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>single_channel_random-multi</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>single-single</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>single-multi</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-single</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>multiple_channels_uncategorized-multi</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>single_block-single</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>single_block-multi</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-single</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>quasi_shattered_channel-multi</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>skip_4-single</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>skip_4-multi</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>same_row-single</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>same_row-multi</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-single</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>multi_channel_block-multi</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>rectangles-single</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>rectangles-multi</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>full_channels-single</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>full_channels-multi</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="B2" t="n">
+        <v>0</v>
+      </c>
+      <c r="C2" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B2" t="n">
+      <c r="D2" t="n">
         <v>3</v>
       </c>
-      <c r="C2" t="n">
+      <c r="E2" t="n">
         <v>64</v>
       </c>
-      <c r="D2" t="n">
+      <c r="F2" t="n">
         <v>32</v>
       </c>
-      <c r="E2" t="n">
+      <c r="G2" t="n">
         <v>11</v>
       </c>
-      <c r="F2" t="n">
+      <c r="H2" t="n">
         <v>2</v>
       </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>0.9991975471150696</v>
       </c>
-      <c r="H2" t="n">
+      <c r="J2" t="n">
         <v>0.0008005614541229</v>
       </c>
-      <c r="I2" t="n">
+      <c r="K2" t="n">
         <v>1.878369262987541e-06</v>
       </c>
-      <c r="J2" t="n">
+      <c r="L2" t="n">
         <v>0.0878434595002888</v>
       </c>
-      <c r="K2" t="n">
+      <c r="M2" t="n">
         <v>0.8168137926088318</v>
       </c>
-      <c r="L2" t="n">
+      <c r="N2" t="n">
         <v>0.0313080389917167</v>
       </c>
-      <c r="M2" t="n">
+      <c r="O2" t="n">
         <v>0.0013722686219021</v>
       </c>
-      <c r="N2" t="n">
+      <c r="P2" t="n">
         <v>0.0156644912957602</v>
       </c>
-      <c r="O2" t="n">
+      <c r="Q2" t="n">
         <v>0.0469579305499185</v>
       </c>
-      <c r="P2" t="n">
+      <c r="R2" t="n">
         <v>2.366511540007909e-06</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="S2" t="n">
         <v>3.21353449367923e-05</v>
       </c>
-      <c r="R2" t="n">
+      <c r="T2" t="n">
         <v>8.127366864892824e-07</v>
       </c>
-      <c r="S2" t="n">
+      <c r="U2" t="n">
         <v>4.267201065757917e-06</v>
       </c>
-      <c r="T2" t="n">
+      <c r="V2" t="n">
         <v>4.062506508837567e-07</v>
       </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
@@ -739,10 +744,10 @@
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
@@ -754,19 +759,19 @@
         <v>0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH2" t="n">
         <v>0</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
@@ -778,99 +783,105 @@
         <v>0</v>
       </c>
       <c r="AM2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN2" t="n">
         <v>0</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS2" t="n">
         <v>0.1113504248635288</v>
       </c>
-      <c r="AR2" t="n">
+      <c r="AT2" t="n">
         <v>0.8886495751364712</v>
       </c>
-      <c r="AS2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT2" t="n">
+      <c r="AU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV2" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B3" t="n">
+      <c r="D3" t="n">
         <v>64</v>
       </c>
-      <c r="C3" t="n">
+      <c r="E3" t="n">
         <v>192</v>
       </c>
-      <c r="D3" t="n">
+      <c r="F3" t="n">
         <v>12</v>
       </c>
-      <c r="E3" t="n">
+      <c r="G3" t="n">
         <v>5</v>
       </c>
-      <c r="F3" t="n">
+      <c r="H3" t="n">
         <v>2</v>
       </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>0.9986701951756304</v>
       </c>
-      <c r="H3" t="n">
+      <c r="J3" t="n">
         <v>0.0013277994797013</v>
       </c>
-      <c r="I3" t="n">
+      <c r="K3" t="n">
         <v>1.992283123832815e-06</v>
       </c>
-      <c r="J3" t="n">
+      <c r="L3" t="n">
         <v>0.0506987974226653</v>
       </c>
-      <c r="K3" t="n">
+      <c r="M3" t="n">
         <v>0.8403391379221128</v>
       </c>
-      <c r="L3" t="n">
+      <c r="N3" t="n">
         <v>0.089076374012618</v>
       </c>
-      <c r="M3" t="n">
+      <c r="O3" t="n">
         <v>0.0128017127800092</v>
       </c>
-      <c r="N3" t="n">
+      <c r="P3" t="n">
         <v>3.108259022974845e-06</v>
       </c>
-      <c r="O3" t="n">
+      <c r="Q3" t="n">
         <v>0.0068480620342423</v>
       </c>
-      <c r="P3" t="n">
+      <c r="R3" t="n">
         <v>4.754089233677841e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="S3" t="n">
         <v>1.456419122010021e-05</v>
       </c>
-      <c r="R3" t="n">
+      <c r="T3" t="n">
         <v>3.525717291754731e-06</v>
       </c>
-      <c r="S3" t="n">
+      <c r="U3" t="n">
         <v>0.0002097377345204</v>
       </c>
-      <c r="T3" t="n">
+      <c r="V3" t="n">
         <v>1.82515289528598e-07</v>
       </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
-      <c r="V3" t="n">
-        <v>1</v>
-      </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
@@ -881,10 +892,10 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -896,19 +907,19 @@
         <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>0</v>
       </c>
       <c r="AG3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH3" t="n">
         <v>0</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
@@ -920,99 +931,105 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS3" t="n">
         <v>0.1113444759371124</v>
       </c>
-      <c r="AR3" t="n">
+      <c r="AT3" t="n">
         <v>0.8886555240628875</v>
       </c>
-      <c r="AS3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="n">
+      <c r="AU3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV3" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv3</t>
         </is>
       </c>
-      <c r="B4" t="n">
+      <c r="D4" t="n">
         <v>192</v>
       </c>
-      <c r="C4" t="n">
+      <c r="E4" t="n">
         <v>384</v>
       </c>
-      <c r="D4" t="n">
+      <c r="F4" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
+      <c r="G4" t="n">
         <v>3</v>
       </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
         <v>0.999573400330842</v>
       </c>
-      <c r="H4" t="n">
+      <c r="J4" t="n">
         <v>0.0004243097048239</v>
       </c>
-      <c r="I4" t="n">
+      <c r="K4" t="n">
         <v>2.276902789690739e-06</v>
       </c>
-      <c r="J4" t="n">
+      <c r="L4" t="n">
         <v>0.0003301062947583</v>
       </c>
-      <c r="K4" t="n">
+      <c r="M4" t="n">
         <v>0.8896982412200412</v>
       </c>
-      <c r="L4" t="n">
+      <c r="N4" t="n">
         <v>0.0391344317597202</v>
       </c>
-      <c r="M4" t="n">
+      <c r="O4" t="n">
         <v>0.0062044898834172</v>
       </c>
-      <c r="N4" t="n">
+      <c r="P4" t="n">
         <v>0.0469739772703896</v>
       </c>
-      <c r="O4" t="n">
+      <c r="Q4" t="n">
         <v>0.0156530212560535</v>
       </c>
-      <c r="P4" t="n">
+      <c r="R4" t="n">
         <v>5.146526553332772e-06</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="S4" t="n">
         <v>3.635458874640003e-05</v>
       </c>
-      <c r="R4" t="n">
+      <c r="T4" t="n">
         <v>0.0016340873192272</v>
       </c>
-      <c r="S4" t="n">
+      <c r="U4" t="n">
         <v>0.0003287828974933</v>
       </c>
-      <c r="T4" t="n">
+      <c r="V4" t="n">
         <v>1.335351546184232e-06</v>
       </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>1</v>
-      </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
@@ -1023,10 +1040,10 @@
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -1038,123 +1055,129 @@
         <v>0</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF4" t="n">
         <v>0</v>
       </c>
       <c r="AG4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH4" t="n">
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ4" t="n">
         <v>0</v>
       </c>
       <c r="AK4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM4" t="n">
         <v>0.6574653291876419</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AN4" t="n">
         <v>0.3425346708123581</v>
       </c>
-      <c r="AM4" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>0</v>
-      </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS4" t="n">
         <v>0.1113244558408738</v>
       </c>
-      <c r="AR4" t="n">
+      <c r="AT4" t="n">
         <v>0.8886755441591262</v>
       </c>
-      <c r="AS4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT4" t="n">
+      <c r="AU4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV4" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" t="n">
+        <v>3</v>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv4</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="D5" t="n">
         <v>384</v>
       </c>
-      <c r="C5" t="n">
+      <c r="E5" t="n">
         <v>256</v>
       </c>
-      <c r="D5" t="n">
+      <c r="F5" t="n">
         <v>5</v>
       </c>
-      <c r="E5" t="n">
+      <c r="G5" t="n">
         <v>3</v>
       </c>
-      <c r="F5" t="n">
-        <v>1</v>
-      </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>0.9990612380563292</v>
       </c>
-      <c r="H5" t="n">
+      <c r="J5" t="n">
         <v>0.0009365656434828</v>
       </c>
-      <c r="I5" t="n">
+      <c r="K5" t="n">
         <v>2.18323864357897e-06</v>
       </c>
-      <c r="J5" t="n">
+      <c r="L5" t="n">
         <v>0.0064923047449558</v>
       </c>
-      <c r="K5" t="n">
+      <c r="M5" t="n">
         <v>0.8814956825172966</v>
       </c>
-      <c r="L5" t="n">
+      <c r="N5" t="n">
         <v>0.035572753840585</v>
       </c>
-      <c r="M5" t="n">
+      <c r="O5" t="n">
         <v>0.008094751084821</v>
       </c>
-      <c r="N5" t="n">
+      <c r="P5" t="n">
         <v>0.0430687139935514</v>
       </c>
-      <c r="O5" t="n">
+      <c r="Q5" t="n">
         <v>0.0234796472385033</v>
       </c>
-      <c r="P5" t="n">
+      <c r="R5" t="n">
         <v>2.413725328182118e-06</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="S5" t="n">
         <v>2.981121001491983e-05</v>
       </c>
-      <c r="R5" t="n">
+      <c r="T5" t="n">
         <v>0.0011766869392575</v>
       </c>
-      <c r="S5" t="n">
+      <c r="U5" t="n">
         <v>0.0002341531099069</v>
       </c>
-      <c r="T5" t="n">
+      <c r="V5" t="n">
         <v>0.0003530470999054</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="n">
-        <v>1</v>
-      </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
@@ -1165,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
         <v>0</v>
@@ -1180,123 +1203,129 @@
         <v>0</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>0</v>
       </c>
       <c r="AG5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
         <v>0</v>
       </c>
       <c r="AK5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" t="n">
         <v>0.9949826361973588</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AN5" t="n">
         <v>0.0050173638026413</v>
       </c>
-      <c r="AM5" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>0</v>
-      </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS5" t="n">
         <v>0.1113432147229741</v>
       </c>
-      <c r="AR5" t="n">
+      <c r="AT5" t="n">
         <v>0.8886567852770257</v>
       </c>
-      <c r="AS5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT5" t="n">
+      <c r="AU5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV5" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C6" t="inlineStr">
         <is>
           <t>alexnet_cifar10_conv5</t>
         </is>
       </c>
-      <c r="B6" t="n">
+      <c r="D6" t="n">
         <v>256</v>
       </c>
-      <c r="C6" t="n">
+      <c r="E6" t="n">
         <v>256</v>
       </c>
-      <c r="D6" t="n">
+      <c r="F6" t="n">
         <v>5</v>
       </c>
-      <c r="E6" t="n">
+      <c r="G6" t="n">
         <v>3</v>
       </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
         <v>0.9994716259303384</v>
       </c>
-      <c r="H6" t="n">
+      <c r="J6" t="n">
         <v>0.0005261298892054</v>
       </c>
-      <c r="I6" t="n">
+      <c r="K6" t="n">
         <v>2.231118911880177e-06</v>
       </c>
-      <c r="J6" t="n">
+      <c r="L6" t="n">
         <v>0.004620684769454</v>
       </c>
-      <c r="K6" t="n">
+      <c r="M6" t="n">
         <v>0.9132902756264488</v>
       </c>
-      <c r="L6" t="n">
+      <c r="N6" t="n">
         <v>0.018511240717825</v>
       </c>
-      <c r="M6" t="n">
+      <c r="O6" t="n">
         <v>0.0076088781756546</v>
       </c>
-      <c r="N6" t="n">
+      <c r="P6" t="n">
         <v>0.0456827506316738</v>
       </c>
-      <c r="O6" t="n">
+      <c r="Q6" t="n">
         <v>0.009131382519462199</v>
       </c>
-      <c r="P6" t="n">
+      <c r="R6" t="n">
         <v>9.527011706447584e-07</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="S6" t="n">
         <v>2.630704408625174e-05</v>
       </c>
-      <c r="R6" t="n">
+      <c r="T6" t="n">
         <v>0.0005027203278329001</v>
       </c>
-      <c r="S6" t="n">
+      <c r="U6" t="n">
         <v>8.295093663139099e-07</v>
       </c>
-      <c r="T6" t="n">
+      <c r="V6" t="n">
         <v>0.0006239376566055</v>
       </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>1</v>
-      </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
@@ -1307,10 +1336,10 @@
         <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB6" t="n">
         <v>0</v>
@@ -1322,123 +1351,129 @@
         <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
         <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" t="n">
         <v>0.9934131969296984</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AN6" t="n">
         <v>0.0065868030703015</v>
       </c>
-      <c r="AM6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>0</v>
-      </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS6" t="n">
         <v>0.111029911509987</v>
       </c>
-      <c r="AR6" t="n">
+      <c r="AT6" t="n">
         <v>0.888970088490013</v>
       </c>
-      <c r="AS6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="AU6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="A7" s="1" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv1</t>
         </is>
       </c>
-      <c r="B7" t="n">
+      <c r="D7" t="n">
         <v>3</v>
       </c>
-      <c r="C7" t="n">
+      <c r="E7" t="n">
         <v>32</v>
       </c>
-      <c r="D7" t="n">
+      <c r="F7" t="n">
         <v>32</v>
       </c>
-      <c r="E7" t="n">
+      <c r="G7" t="n">
         <v>3</v>
       </c>
-      <c r="F7" t="n">
-        <v>1</v>
-      </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
+        <v>1</v>
+      </c>
+      <c r="I7" t="n">
         <v>0.9994082408130508</v>
       </c>
-      <c r="H7" t="n">
+      <c r="J7" t="n">
         <v>0.0005897996863628</v>
       </c>
-      <c r="I7" t="n">
+      <c r="K7" t="n">
         <v>1.946439042070148e-06</v>
       </c>
-      <c r="J7" t="n">
+      <c r="L7" t="n">
         <v>0.1753294923476672</v>
       </c>
-      <c r="K7" t="n">
+      <c r="M7" t="n">
         <v>0.7351684291541376</v>
       </c>
-      <c r="L7" t="n">
+      <c r="N7" t="n">
         <v>0.021917101589674</v>
       </c>
-      <c r="M7" t="n">
+      <c r="O7" t="n">
         <v>0.001730768635938</v>
       </c>
-      <c r="N7" t="n">
+      <c r="P7" t="n">
         <v>0.0328858469255085</v>
       </c>
-      <c r="O7" t="n">
+      <c r="Q7" t="n">
         <v>0.0328705655205616</v>
       </c>
-      <c r="P7" t="n">
+      <c r="R7" t="n">
         <v>1.345154708736929e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="S7" t="n">
         <v>9.311348683251664e-05</v>
       </c>
-      <c r="R7" t="n">
+      <c r="T7" t="n">
         <v>6.241101708977771e-07</v>
       </c>
-      <c r="S7" t="n">
+      <c r="U7" t="n">
         <v>2.496752327456661e-06</v>
       </c>
-      <c r="T7" t="n">
+      <c r="V7" t="n">
         <v>2.032609289285583e-07</v>
       </c>
-      <c r="U7" t="n">
-        <v>0</v>
-      </c>
-      <c r="V7" t="n">
-        <v>1</v>
-      </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
@@ -1449,10 +1484,10 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
@@ -1464,19 +1499,19 @@
         <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF7" t="n">
         <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ7" t="n">
         <v>0</v>
@@ -1485,102 +1520,108 @@
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS7" t="n">
         <v>0.1115502018549213</v>
       </c>
-      <c r="AR7" t="n">
+      <c r="AT7" t="n">
         <v>0.8884497981450786</v>
       </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="A8" s="1" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" t="n">
+        <v>6</v>
+      </c>
+      <c r="C8" t="inlineStr">
         <is>
           <t>lenet_cifar10_conv2</t>
         </is>
       </c>
-      <c r="B8" t="n">
+      <c r="D8" t="n">
         <v>32</v>
       </c>
-      <c r="C8" t="n">
+      <c r="E8" t="n">
         <v>64</v>
       </c>
-      <c r="D8" t="n">
+      <c r="F8" t="n">
         <v>16</v>
       </c>
-      <c r="E8" t="n">
+      <c r="G8" t="n">
         <v>3</v>
       </c>
-      <c r="F8" t="n">
-        <v>1</v>
-      </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
+        <v>1</v>
+      </c>
+      <c r="I8" t="n">
         <v>0.9992838816750572</v>
       </c>
-      <c r="H8" t="n">
+      <c r="J8" t="n">
         <v>0.0007140496039309</v>
       </c>
-      <c r="I8" t="n">
+      <c r="K8" t="n">
         <v>2.05565946756158e-06</v>
       </c>
-      <c r="J8" t="n">
+      <c r="L8" t="n">
         <v>0.0441470046152142</v>
       </c>
-      <c r="K8" t="n">
+      <c r="M8" t="n">
         <v>0.8496980824933247</v>
       </c>
-      <c r="L8" t="n">
+      <c r="N8" t="n">
         <v>0.0634366739301359</v>
       </c>
-      <c r="M8" t="n">
+      <c r="O8" t="n">
         <v>0.0077772887530912</v>
       </c>
-      <c r="N8" t="n">
+      <c r="P8" t="n">
         <v>0.0057715727775374</v>
       </c>
-      <c r="O8" t="n">
+      <c r="Q8" t="n">
         <v>0.0230672216613233</v>
       </c>
-      <c r="P8" t="n">
+      <c r="R8" t="n">
         <v>3.840379457708862e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="S8" t="n">
         <v>2.524195969974975e-05</v>
       </c>
-      <c r="R8" t="n">
+      <c r="T8" t="n">
         <v>2.188811191153471e-06</v>
       </c>
-      <c r="S8" t="n">
+      <c r="U8" t="n">
         <v>4.733817519335179e-06</v>
       </c>
-      <c r="T8" t="n">
+      <c r="V8" t="n">
         <v>0.0060661304312059</v>
       </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1</v>
-      </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
@@ -1591,10 +1632,10 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB8" t="n">
         <v>0</v>
@@ -1606,19 +1647,19 @@
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>0</v>
       </c>
       <c r="AG8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH8" t="n">
         <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
@@ -1627,102 +1668,108 @@
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS8" t="n">
         <v>0.1110645068045804</v>
       </c>
-      <c r="AR8" t="n">
+      <c r="AT8" t="n">
         <v>0.8889354931954195</v>
       </c>
-      <c r="AS8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="n">
+      <c r="AU8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="A9" s="1" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" t="n">
+        <v>7</v>
+      </c>
+      <c r="C9" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.1.conv.1</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="D9" t="n">
         <v>32</v>
       </c>
-      <c r="C9" t="n">
+      <c r="E9" t="n">
         <v>16</v>
       </c>
-      <c r="D9" t="n">
+      <c r="F9" t="n">
         <v>16</v>
       </c>
-      <c r="E9" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0</v>
-      </c>
       <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" t="n">
         <v>0.9995612056103144</v>
       </c>
-      <c r="H9" t="n">
+      <c r="J9" t="n">
         <v>0.0004363789024224</v>
       </c>
-      <c r="I9" t="n">
+      <c r="K9" t="n">
         <v>2.402425718856577e-06</v>
       </c>
-      <c r="J9" t="n">
+      <c r="L9" t="n">
         <v>0.0918955732408166</v>
       </c>
-      <c r="K9" t="n">
+      <c r="M9" t="n">
         <v>0.8092309152267176</v>
       </c>
-      <c r="L9" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" t="n">
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
         <v>0.0013932634021861</v>
       </c>
-      <c r="N9" t="n">
+      <c r="P9" t="n">
         <v>4.781858073715594e-06</v>
       </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
-      <c r="P9" t="n">
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R9" t="n">
         <v>3.836179335948823e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="S9" t="n">
         <v>0.09745985298198689</v>
       </c>
-      <c r="R9" t="n">
+      <c r="T9" t="n">
         <v>1.831687273241637e-06</v>
       </c>
-      <c r="S9" t="n">
+      <c r="U9" t="n">
         <v>8.750212350802884e-06</v>
       </c>
-      <c r="T9" t="n">
+      <c r="V9" t="n">
         <v>1.182149714695386e-06</v>
       </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1</v>
-      </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
@@ -1733,10 +1780,10 @@
         <v>0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB9" t="n">
         <v>0</v>
@@ -1748,19 +1795,19 @@
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
@@ -1772,98 +1819,104 @@
         <v>0</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
         <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ9" t="n">
         <v>0</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
       </c>
       <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="A10" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" t="n">
+        <v>8</v>
+      </c>
+      <c r="C10" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.10.conv.2</t>
         </is>
       </c>
-      <c r="B10" t="n">
+      <c r="D10" t="n">
         <v>384</v>
       </c>
-      <c r="C10" t="n">
+      <c r="E10" t="n">
         <v>64</v>
       </c>
-      <c r="D10" t="n">
+      <c r="F10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
       <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
         <v>0.999793350780705</v>
       </c>
-      <c r="H10" t="n">
+      <c r="J10" t="n">
         <v>0.0002043711655386</v>
       </c>
-      <c r="I10" t="n">
+      <c r="K10" t="n">
         <v>2.264992211973501e-06</v>
       </c>
-      <c r="J10" t="n">
+      <c r="L10" t="n">
         <v>0.0021206176578535</v>
       </c>
-      <c r="K10" t="n">
+      <c r="M10" t="n">
         <v>0.9612878949627652</v>
       </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
         <v>0.0021106161398902</v>
       </c>
-      <c r="N10" t="n">
+      <c r="P10" t="n">
         <v>1.310369452505643e-05</v>
       </c>
-      <c r="O10" t="n">
+      <c r="Q10" t="n">
         <v>8.420824009037253e-08</v>
       </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="n">
         <v>0.0328823957987306</v>
       </c>
-      <c r="R10" t="n">
+      <c r="T10" t="n">
         <v>0.0015852744764507</v>
       </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
-      <c r="T10" t="n">
-        <v>0</v>
-      </c>
       <c r="U10" t="n">
         <v>0</v>
       </c>
       <c r="V10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
@@ -1875,10 +1928,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
@@ -1890,7 +1943,7 @@
         <v>0</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF10" t="n">
         <v>0</v>
@@ -1914,13 +1967,13 @@
         <v>0</v>
       </c>
       <c r="AM10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN10" t="n">
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
         <v>0</v>
@@ -1935,77 +1988,83 @@
         <v>0</v>
       </c>
       <c r="AT10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="A11" s="1" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C11" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.12.conv.0.0</t>
         </is>
       </c>
-      <c r="B11" t="n">
+      <c r="D11" t="n">
         <v>96</v>
       </c>
-      <c r="C11" t="n">
+      <c r="E11" t="n">
         <v>576</v>
       </c>
-      <c r="D11" t="n">
+      <c r="F11" t="n">
         <v>8</v>
       </c>
-      <c r="E11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0</v>
-      </c>
       <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" t="n">
         <v>0.999953263176279</v>
       </c>
-      <c r="H11" t="n">
+      <c r="J11" t="n">
         <v>4.450274029329908e-05</v>
       </c>
-      <c r="I11" t="n">
+      <c r="K11" t="n">
         <v>2.221021883335285e-06</v>
       </c>
-      <c r="J11" t="n">
+      <c r="L11" t="n">
         <v>1.864912969121469e-05</v>
       </c>
-      <c r="K11" t="n">
+      <c r="M11" t="n">
         <v>0.8981697403577256</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="n">
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
         <v>0.0021106469713648</v>
       </c>
-      <c r="N11" t="n">
+      <c r="P11" t="n">
         <v>0.09967682714471179</v>
       </c>
-      <c r="O11" t="n">
+      <c r="Q11" t="n">
         <v>5.025329055037027e-09</v>
       </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="n">
         <v>1.828844786861276e-05</v>
       </c>
-      <c r="R11" t="n">
+      <c r="T11" t="n">
         <v>5.829861764382279e-06</v>
       </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
       <c r="U11" t="n">
         <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
@@ -2017,10 +2076,10 @@
         <v>0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
@@ -2032,7 +2091,7 @@
         <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF11" t="n">
         <v>0</v>
@@ -2056,13 +2115,13 @@
         <v>0</v>
       </c>
       <c r="AM11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>0</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -2077,78 +2136,84 @@
         <v>0</v>
       </c>
       <c r="AT11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV11" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" t="n">
+        <v>10</v>
+      </c>
+      <c r="C12" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.2.conv.2</t>
         </is>
       </c>
-      <c r="B12" t="n">
+      <c r="D12" t="n">
         <v>96</v>
       </c>
-      <c r="C12" t="n">
+      <c r="E12" t="n">
         <v>24</v>
       </c>
-      <c r="D12" t="n">
+      <c r="F12" t="n">
         <v>8</v>
       </c>
-      <c r="E12" t="n">
-        <v>1</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0</v>
-      </c>
       <c r="G12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" t="n">
         <v>0.9995801245650228</v>
       </c>
-      <c r="H12" t="n">
+      <c r="J12" t="n">
         <v>0.0004175766292134</v>
       </c>
-      <c r="I12" t="n">
+      <c r="K12" t="n">
         <v>2.285744219596903e-06</v>
       </c>
-      <c r="J12" t="n">
+      <c r="L12" t="n">
         <v>7.426037804591282e-05</v>
       </c>
-      <c r="K12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" t="n">
-        <v>0</v>
-      </c>
       <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
         <v>0.0045914821677496</v>
       </c>
-      <c r="N12" t="n">
+      <c r="P12" t="n">
         <v>1.830559104276112e-06</v>
       </c>
-      <c r="O12" t="n">
+      <c r="Q12" t="n">
         <v>2.904968200239127e-09</v>
       </c>
-      <c r="P12" t="n">
+      <c r="R12" t="n">
         <v>0.886074374007536</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="S12" t="n">
         <v>0.103150750309685</v>
       </c>
-      <c r="R12" t="n">
+      <c r="T12" t="n">
         <v>3.5435572228355e-06</v>
       </c>
-      <c r="S12" t="n">
+      <c r="U12" t="n">
         <v>0.0061022162832867</v>
       </c>
-      <c r="T12" t="n">
+      <c r="V12" t="n">
         <v>1.526770857003524e-06</v>
       </c>
-      <c r="U12" t="n">
-        <v>0</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
@@ -2159,10 +2224,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
         <v>0</v>
@@ -2174,19 +2239,19 @@
         <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF12" t="n">
         <v>0</v>
       </c>
       <c r="AG12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ12" t="n">
         <v>0</v>
@@ -2198,99 +2263,105 @@
         <v>0</v>
       </c>
       <c r="AM12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
         <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ12" t="n">
         <v>0</v>
       </c>
       <c r="AR12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS12" t="n">
         <v>0</v>
       </c>
       <c r="AT12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="A13" s="1" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" t="n">
+        <v>11</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.0.0</t>
         </is>
       </c>
-      <c r="B13" t="n">
+      <c r="D13" t="n">
         <v>24</v>
       </c>
-      <c r="C13" t="n">
+      <c r="E13" t="n">
         <v>144</v>
       </c>
-      <c r="D13" t="n">
+      <c r="F13" t="n">
         <v>8</v>
       </c>
-      <c r="E13" t="n">
-        <v>1</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0</v>
-      </c>
       <c r="G13" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" t="n">
         <v>0.9999349133295612</v>
       </c>
-      <c r="H13" t="n">
+      <c r="J13" t="n">
         <v>6.275045621555766e-05</v>
       </c>
-      <c r="I13" t="n">
+      <c r="K13" t="n">
         <v>2.32315267899147e-06</v>
       </c>
-      <c r="J13" t="n">
+      <c r="L13" t="n">
         <v>0.0122477330479631</v>
       </c>
-      <c r="K13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
         <v>1.245524918182234e-07</v>
       </c>
-      <c r="M13" t="n">
+      <c r="O13" t="n">
         <v>1.239790705342687e-05</v>
       </c>
-      <c r="N13" t="n">
+      <c r="P13" t="n">
         <v>3.134288724091342e-06</v>
       </c>
-      <c r="O13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P13" t="n">
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>0.987680189753848</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="S13" t="n">
         <v>1.394154935638847e-05</v>
       </c>
-      <c r="R13" t="n">
+      <c r="T13" t="n">
         <v>4.983399388942951e-06</v>
       </c>
-      <c r="S13" t="n">
+      <c r="U13" t="n">
         <v>3.64790097258392e-05</v>
       </c>
-      <c r="T13" t="n">
+      <c r="V13" t="n">
         <v>1.003429903848309e-06</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1</v>
-      </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
@@ -2301,10 +2372,10 @@
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
         <v>0</v>
@@ -2316,19 +2387,19 @@
         <v>0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ13" t="n">
         <v>0</v>
@@ -2340,99 +2411,105 @@
         <v>0</v>
       </c>
       <c r="AM13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
         <v>0</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ13" t="n">
         <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS13" t="n">
         <v>0</v>
       </c>
       <c r="AT13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV13" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="A14" s="1" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" t="n">
+        <v>12</v>
+      </c>
+      <c r="C14" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.3.conv.2</t>
         </is>
       </c>
-      <c r="B14" t="n">
+      <c r="D14" t="n">
         <v>144</v>
       </c>
-      <c r="C14" t="n">
+      <c r="E14" t="n">
         <v>24</v>
       </c>
-      <c r="D14" t="n">
+      <c r="F14" t="n">
         <v>4</v>
       </c>
-      <c r="E14" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0</v>
-      </c>
       <c r="G14" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" t="n">
         <v>0.9995234281031916</v>
       </c>
-      <c r="H14" t="n">
+      <c r="J14" t="n">
         <v>0.0004742154134557</v>
       </c>
-      <c r="I14" t="n">
+      <c r="K14" t="n">
         <v>2.34342180840744e-06</v>
       </c>
-      <c r="J14" t="n">
+      <c r="L14" t="n">
         <v>0.0540312689791262</v>
       </c>
-      <c r="K14" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" t="n">
-        <v>0</v>
-      </c>
       <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="n">
         <v>0.009506240974247401</v>
       </c>
-      <c r="N14" t="n">
+      <c r="P14" t="n">
         <v>3.146784343203964e-06</v>
       </c>
-      <c r="O14" t="n">
+      <c r="Q14" t="n">
         <v>3.608319758278884e-07</v>
       </c>
-      <c r="P14" t="n">
+      <c r="R14" t="n">
         <v>0.8338677080991113</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="S14" t="n">
         <v>0.1004661723500226</v>
       </c>
-      <c r="R14" t="n">
+      <c r="T14" t="n">
         <v>5.550924446152859e-06</v>
       </c>
-      <c r="S14" t="n">
+      <c r="U14" t="n">
         <v>0.002118989651636</v>
       </c>
-      <c r="T14" t="n">
+      <c r="V14" t="n">
         <v>5.483435466754749e-07</v>
       </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1</v>
-      </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
@@ -2443,10 +2520,10 @@
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
         <v>0</v>
@@ -2458,19 +2535,19 @@
         <v>0</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF14" t="n">
         <v>0</v>
       </c>
       <c r="AG14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH14" t="n">
         <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -2482,99 +2559,105 @@
         <v>0</v>
       </c>
       <c r="AM14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN14" t="n">
         <v>0</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ14" t="n">
         <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS14" t="n">
         <v>0</v>
       </c>
       <c r="AT14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="A15" s="1" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" t="n">
+        <v>13</v>
+      </c>
+      <c r="C15" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.4.conv.0.0</t>
         </is>
       </c>
-      <c r="B15" t="n">
+      <c r="D15" t="n">
         <v>24</v>
       </c>
-      <c r="C15" t="n">
+      <c r="E15" t="n">
         <v>144</v>
       </c>
-      <c r="D15" t="n">
+      <c r="F15" t="n">
         <v>4</v>
       </c>
-      <c r="E15" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0</v>
-      </c>
       <c r="G15" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" t="n">
         <v>0.999924587250918</v>
       </c>
-      <c r="H15" t="n">
+      <c r="J15" t="n">
         <v>7.304631242335402e-05</v>
       </c>
-      <c r="I15" t="n">
+      <c r="K15" t="n">
         <v>2.353375114201529e-06</v>
       </c>
-      <c r="J15" t="n">
+      <c r="L15" t="n">
         <v>7.119143629388023e-05</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0</v>
-      </c>
       <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
         <v>1.088265217126682e-05</v>
       </c>
-      <c r="N15" t="n">
+      <c r="P15" t="n">
         <v>2.384931544533358e-06</v>
       </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
         <v>0.9779438919748032</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="S15" t="n">
         <v>0.0137096537741524</v>
       </c>
-      <c r="R15" t="n">
+      <c r="T15" t="n">
         <v>4.972702642162133e-06</v>
       </c>
-      <c r="S15" t="n">
+      <c r="U15" t="n">
         <v>0.0082560359609968</v>
       </c>
-      <c r="T15" t="n">
+      <c r="V15" t="n">
         <v>9.735058511936805e-07</v>
       </c>
-      <c r="U15" t="n">
-        <v>0</v>
-      </c>
-      <c r="V15" t="n">
-        <v>1</v>
-      </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
@@ -2585,10 +2668,10 @@
         <v>0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB15" t="n">
         <v>0</v>
@@ -2600,19 +2683,19 @@
         <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH15" t="n">
         <v>0</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ15" t="n">
         <v>0</v>
@@ -2624,99 +2707,105 @@
         <v>0</v>
       </c>
       <c r="AM15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN15" t="n">
         <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ15" t="n">
         <v>0</v>
       </c>
       <c r="AR15" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS15" t="n">
         <v>0</v>
       </c>
       <c r="AT15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV15" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="A16" s="1" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.0.0</t>
         </is>
       </c>
-      <c r="B16" t="n">
+      <c r="D16" t="n">
         <v>32</v>
       </c>
-      <c r="C16" t="n">
+      <c r="E16" t="n">
         <v>192</v>
       </c>
-      <c r="D16" t="n">
+      <c r="F16" t="n">
         <v>4</v>
       </c>
-      <c r="E16" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0</v>
-      </c>
       <c r="G16" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" t="n">
         <v>0.9999521494606316</v>
       </c>
-      <c r="H16" t="n">
+      <c r="J16" t="n">
         <v>4.559166776333455e-05</v>
       </c>
-      <c r="I16" t="n">
+      <c r="K16" t="n">
         <v>2.24581006064638e-06</v>
       </c>
-      <c r="J16" t="n">
+      <c r="L16" t="n">
         <v>3.917360580208432e-05</v>
       </c>
-      <c r="K16" t="n">
+      <c r="M16" t="n">
         <v>6.135151761600983e-06</v>
       </c>
-      <c r="L16" t="n">
+      <c r="N16" t="n">
         <v>1.649670574746197e-07</v>
       </c>
-      <c r="M16" t="n">
+      <c r="O16" t="n">
         <v>1.285866762698271e-05</v>
       </c>
-      <c r="N16" t="n">
+      <c r="P16" t="n">
         <v>4.903323055454054e-06</v>
       </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="n">
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.986344780537576</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="S16" t="n">
         <v>0.0121858038913592</v>
       </c>
-      <c r="R16" t="n">
+      <c r="T16" t="n">
         <v>6.934441071547352e-06</v>
       </c>
-      <c r="S16" t="n">
+      <c r="U16" t="n">
         <v>0.0013982188362234</v>
       </c>
-      <c r="T16" t="n">
+      <c r="V16" t="n">
         <v>1.01351692184967e-06</v>
       </c>
-      <c r="U16" t="n">
-        <v>0</v>
-      </c>
-      <c r="V16" t="n">
-        <v>1</v>
-      </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
@@ -2727,10 +2816,10 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2742,19 +2831,19 @@
         <v>0</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF16" t="n">
         <v>0</v>
       </c>
       <c r="AG16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH16" t="n">
         <v>0</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ16" t="n">
         <v>0</v>
@@ -2766,99 +2855,105 @@
         <v>0</v>
       </c>
       <c r="AM16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN16" t="n">
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ16" t="n">
         <v>0</v>
       </c>
       <c r="AR16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS16" t="n">
         <v>0</v>
       </c>
       <c r="AT16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="A17" s="1" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="n">
+        <v>15</v>
+      </c>
+      <c r="C17" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.5.conv.2</t>
         </is>
       </c>
-      <c r="B17" t="n">
+      <c r="D17" t="n">
         <v>192</v>
       </c>
-      <c r="C17" t="n">
+      <c r="E17" t="n">
         <v>32</v>
       </c>
-      <c r="D17" t="n">
+      <c r="F17" t="n">
         <v>2</v>
       </c>
-      <c r="E17" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0</v>
-      </c>
       <c r="G17" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>0.999811105723736</v>
       </c>
-      <c r="H17" t="n">
+      <c r="J17" t="n">
         <v>0.0001865735473452</v>
       </c>
-      <c r="I17" t="n">
+      <c r="K17" t="n">
         <v>2.307667374242729e-06</v>
       </c>
-      <c r="J17" t="n">
+      <c r="L17" t="n">
         <v>0.0007374773990412</v>
       </c>
-      <c r="K17" t="n">
+      <c r="M17" t="n">
         <v>0.0028871664645838</v>
       </c>
-      <c r="L17" t="n">
+      <c r="N17" t="n">
         <v>0.0007213064277722</v>
       </c>
-      <c r="M17" t="n">
+      <c r="O17" t="n">
         <v>0.006509296197014</v>
       </c>
-      <c r="N17" t="n">
+      <c r="P17" t="n">
         <v>6.598229036821054e-06</v>
       </c>
-      <c r="O17" t="n">
+      <c r="Q17" t="n">
         <v>8.982674899592562e-07</v>
       </c>
-      <c r="P17" t="n">
+      <c r="R17" t="n">
         <v>0.9371340415397512</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="S17" t="n">
         <v>0.0498255637101531</v>
       </c>
-      <c r="R17" t="n">
+      <c r="T17" t="n">
         <v>6.500431731527001e-06</v>
       </c>
-      <c r="S17" t="n">
+      <c r="U17" t="n">
         <v>0.0007262095783689</v>
       </c>
-      <c r="T17" t="n">
+      <c r="V17" t="n">
         <v>0.0014449286935125</v>
       </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
@@ -2869,10 +2964,10 @@
         <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
         <v>0</v>
@@ -2884,25 +2979,25 @@
         <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="n">
         <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
         <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ17" t="n">
         <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
         <v>0</v>
@@ -2914,93 +3009,99 @@
         <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV17" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="A18" s="1" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="n">
+        <v>16</v>
+      </c>
+      <c r="C18" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.6.conv.0.0</t>
         </is>
       </c>
-      <c r="B18" t="n">
+      <c r="D18" t="n">
         <v>32</v>
       </c>
-      <c r="C18" t="n">
+      <c r="E18" t="n">
         <v>192</v>
       </c>
-      <c r="D18" t="n">
+      <c r="F18" t="n">
         <v>2</v>
       </c>
-      <c r="E18" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0</v>
-      </c>
       <c r="G18" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="n">
         <v>0.9999795799179512</v>
       </c>
-      <c r="H18" t="n">
+      <c r="J18" t="n">
         <v>1.81856185804048e-05</v>
       </c>
-      <c r="I18" t="n">
+      <c r="K18" t="n">
         <v>2.221401924245514e-06</v>
       </c>
-      <c r="J18" t="n">
+      <c r="L18" t="n">
         <v>4.337866645963501e-05</v>
       </c>
-      <c r="K18" t="n">
+      <c r="M18" t="n">
         <v>5.317699777832803e-06</v>
       </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
         <v>1.417263900418109e-05</v>
       </c>
-      <c r="N18" t="n">
+      <c r="P18" t="n">
         <v>4.678961762162195e-06</v>
       </c>
-      <c r="O18" t="n">
+      <c r="Q18" t="n">
         <v>5.965777920310406e-11</v>
       </c>
-      <c r="P18" t="n">
+      <c r="R18" t="n">
         <v>0.9953215116392704</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="S18" t="n">
         <v>1.130272343224036e-05</v>
       </c>
-      <c r="R18" t="n">
+      <c r="T18" t="n">
         <v>5.757295313447367e-06</v>
       </c>
-      <c r="S18" t="n">
+      <c r="U18" t="n">
         <v>0.004591985807004</v>
       </c>
-      <c r="T18" t="n">
+      <c r="V18" t="n">
         <v>1.881446773749673e-06</v>
       </c>
-      <c r="U18" t="n">
-        <v>0</v>
-      </c>
-      <c r="V18" t="n">
-        <v>1</v>
-      </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
@@ -3011,10 +3112,10 @@
         <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
@@ -3026,19 +3127,19 @@
         <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
         <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ18" t="n">
         <v>0</v>
@@ -3050,98 +3151,104 @@
         <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
         <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
         <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS18" t="n">
         <v>0</v>
       </c>
       <c r="AT18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="A19" s="1" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="n">
+        <v>17</v>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.7.conv.2</t>
         </is>
       </c>
-      <c r="B19" t="n">
+      <c r="D19" t="n">
         <v>192</v>
       </c>
-      <c r="C19" t="n">
+      <c r="E19" t="n">
         <v>64</v>
       </c>
-      <c r="D19" t="n">
+      <c r="F19" t="n">
         <v>2</v>
       </c>
-      <c r="E19" t="n">
-        <v>1</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
       <c r="G19" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" t="n">
         <v>0.9998542138158882</v>
       </c>
-      <c r="H19" t="n">
+      <c r="J19" t="n">
         <v>0.0001434648749357</v>
       </c>
-      <c r="I19" t="n">
+      <c r="K19" t="n">
         <v>2.308247631640014e-06</v>
       </c>
-      <c r="J19" t="n">
+      <c r="L19" t="n">
         <v>2.375125604286222e-05</v>
       </c>
-      <c r="K19" t="n">
+      <c r="M19" t="n">
         <v>0.9631550444220917</v>
       </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.0013097737524837</v>
       </c>
-      <c r="N19" t="n">
+      <c r="P19" t="n">
         <v>3.252473180627455e-06</v>
       </c>
-      <c r="O19" t="n">
+      <c r="Q19" t="n">
         <v>1.216112603338691e-08</v>
       </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>0.0328934134361175</v>
       </c>
-      <c r="R19" t="n">
+      <c r="T19" t="n">
         <v>0.0026147394374131</v>
       </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
@@ -3153,10 +3260,10 @@
         <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -3168,7 +3275,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="n">
         <v>0</v>
@@ -3192,13 +3299,13 @@
         <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
         <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP19" t="n">
         <v>0</v>
@@ -3213,77 +3320,83 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV19" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="A20" s="1" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="n">
+        <v>18</v>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.8.conv.0.0</t>
         </is>
       </c>
-      <c r="B20" t="n">
+      <c r="D20" t="n">
         <v>64</v>
       </c>
-      <c r="C20" t="n">
+      <c r="E20" t="n">
         <v>384</v>
       </c>
-      <c r="D20" t="n">
+      <c r="F20" t="n">
         <v>2</v>
       </c>
-      <c r="E20" t="n">
-        <v>1</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0</v>
-      </c>
       <c r="G20" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" t="n">
         <v>0.9999272398061402</v>
       </c>
-      <c r="H20" t="n">
+      <c r="J20" t="n">
         <v>7.058027941112731e-05</v>
       </c>
-      <c r="I20" t="n">
+      <c r="K20" t="n">
         <v>2.166852904335762e-06</v>
       </c>
-      <c r="J20" t="n">
+      <c r="L20" t="n">
         <v>0.0015343937649566</v>
       </c>
-      <c r="K20" t="n">
+      <c r="M20" t="n">
         <v>0.9847414716930338</v>
       </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
         <v>2.358807812194662e-06</v>
       </c>
-      <c r="N20" t="n">
+      <c r="P20" t="n">
         <v>3.22497820690906e-06</v>
       </c>
-      <c r="O20" t="n">
+      <c r="Q20" t="n">
         <v>7.831276487546329e-09</v>
       </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>0.0121911748074265</v>
       </c>
-      <c r="R20" t="n">
+      <c r="T20" t="n">
         <v>0.0015273550557431</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
-      <c r="T20" t="n">
-        <v>0</v>
-      </c>
       <c r="U20" t="n">
         <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
@@ -3295,10 +3408,10 @@
         <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -3310,7 +3423,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="n">
         <v>0</v>
@@ -3334,13 +3447,13 @@
         <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
         <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP20" t="n">
         <v>0</v>
@@ -3355,77 +3468,83 @@
         <v>0</v>
       </c>
       <c r="AT20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="A21" s="1" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" t="inlineStr">
         <is>
           <t>mobilenetv2_gtsrb_features.9.conv.2</t>
         </is>
       </c>
-      <c r="B21" t="n">
+      <c r="D21" t="n">
         <v>384</v>
       </c>
-      <c r="C21" t="n">
+      <c r="E21" t="n">
         <v>64</v>
       </c>
-      <c r="D21" t="n">
+      <c r="F21" t="n">
         <v>2</v>
       </c>
-      <c r="E21" t="n">
-        <v>1</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0</v>
-      </c>
       <c r="G21" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
         <v>0.9997959884323204</v>
       </c>
-      <c r="H21" t="n">
+      <c r="J21" t="n">
         <v>0.0002018128999933</v>
       </c>
-      <c r="I21" t="n">
+      <c r="K21" t="n">
         <v>2.185606141702294e-06</v>
       </c>
-      <c r="J21" t="n">
+      <c r="L21" t="n">
         <v>0.0044361887073789</v>
       </c>
-      <c r="K21" t="n">
+      <c r="M21" t="n">
         <v>0.975636210393293</v>
       </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
         <v>0.0039832626599446</v>
       </c>
-      <c r="N21" t="n">
+      <c r="P21" t="n">
         <v>1.139510924684068e-05</v>
       </c>
-      <c r="O21" t="n">
+      <c r="Q21" t="n">
         <v>4.603469791554834e-07</v>
       </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="n">
         <v>0.0137150689226327</v>
       </c>
-      <c r="R21" t="n">
+      <c r="T21" t="n">
         <v>0.0022174007989804</v>
       </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
-      <c r="T21" t="n">
-        <v>0</v>
-      </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
@@ -3437,10 +3556,10 @@
         <v>0</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB21" t="n">
         <v>0</v>
@@ -3452,7 +3571,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="n">
         <v>0</v>
@@ -3476,13 +3595,13 @@
         <v>0</v>
       </c>
       <c r="AM21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN21" t="n">
         <v>0</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP21" t="n">
         <v>0</v>
@@ -3497,77 +3616,83 @@
         <v>0</v>
       </c>
       <c r="AT21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU21" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV21" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="A22" s="1" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="n">
+        <v>20</v>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>res50_cifar10_layer1.2.conv1</t>
         </is>
       </c>
-      <c r="B22" t="n">
+      <c r="D22" t="n">
         <v>256</v>
       </c>
-      <c r="C22" t="n">
+      <c r="E22" t="n">
         <v>64</v>
       </c>
-      <c r="D22" t="n">
+      <c r="F22" t="n">
         <v>32</v>
       </c>
-      <c r="E22" t="n">
-        <v>1</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
       <c r="G22" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" t="n">
         <v>0.6876122490635312</v>
       </c>
-      <c r="H22" t="n">
+      <c r="J22" t="n">
         <v>0.3123855519867539</v>
       </c>
-      <c r="I22" t="n">
+      <c r="K22" t="n">
         <v>2.185888170510363e-06</v>
       </c>
-      <c r="J22" t="n">
+      <c r="L22" t="n">
         <v>0.0001214651094429</v>
       </c>
-      <c r="K22" t="n">
+      <c r="M22" t="n">
         <v>0.9985773268196142</v>
       </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
         <v>7.523788682766903e-08</v>
       </c>
-      <c r="N22" t="n">
+      <c r="P22" t="n">
         <v>2.188166900520592e-07</v>
       </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
         <v>3.868088182311978e-08</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="S22" t="n">
         <v>0.0013008622496511</v>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="n">
+      <c r="T22" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" t="n">
         <v>2.428858610740443e-11</v>
       </c>
-      <c r="T22" t="n">
-        <v>0</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0</v>
-      </c>
       <c r="V22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
@@ -3579,10 +3704,10 @@
         <v>0</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB22" t="n">
         <v>0</v>
@@ -3594,7 +3719,7 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF22" t="n">
         <v>0</v>
@@ -3639,78 +3764,84 @@
         <v>0</v>
       </c>
       <c r="AT22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="A23" s="1" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="n">
+        <v>21</v>
+      </c>
+      <c r="C23" t="inlineStr">
         <is>
           <t>res50_cifar10_layer2.1.conv1</t>
         </is>
       </c>
-      <c r="B23" t="n">
+      <c r="D23" t="n">
         <v>512</v>
       </c>
-      <c r="C23" t="n">
+      <c r="E23" t="n">
         <v>128</v>
       </c>
-      <c r="D23" t="n">
+      <c r="F23" t="n">
         <v>16</v>
       </c>
-      <c r="E23" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
       <c r="G23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="n">
         <v>0.6895415817693646</v>
       </c>
-      <c r="H23" t="n">
+      <c r="J23" t="n">
         <v>0.3104560890518303</v>
       </c>
-      <c r="I23" t="n">
+      <c r="K23" t="n">
         <v>2.31611726058967e-06</v>
       </c>
-      <c r="J23" t="n">
+      <c r="L23" t="n">
         <v>2.429430033434606e-05</v>
       </c>
-      <c r="K23" t="n">
+      <c r="M23" t="n">
         <v>0.9994101557329336</v>
       </c>
-      <c r="L23" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" t="n">
+      <c r="N23" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" t="n">
         <v>6.17894669652062e-06</v>
       </c>
-      <c r="N23" t="n">
+      <c r="P23" t="n">
         <v>3.451323108963335e-07</v>
       </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
-      <c r="P23" t="n">
+      <c r="Q23" t="n">
+        <v>0</v>
+      </c>
+      <c r="R23" t="n">
         <v>1.006719284732821e-07</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="S23" t="n">
         <v>0.0005588745522713</v>
       </c>
-      <c r="R23" t="n">
+      <c r="T23" t="n">
         <v>7.246940411030539e-11</v>
       </c>
-      <c r="S23" t="n">
+      <c r="U23" t="n">
         <v>1.87889120499116e-08</v>
       </c>
-      <c r="T23" t="n">
+      <c r="V23" t="n">
         <v>1.874059911383807e-08</v>
       </c>
-      <c r="U23" t="n">
-        <v>0</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1</v>
-      </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
@@ -3721,10 +3852,10 @@
         <v>0</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3736,19 +3867,19 @@
         <v>0</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF23" t="n">
         <v>0</v>
       </c>
       <c r="AG23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH23" t="n">
         <v>0</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ23" t="n">
         <v>0</v>
@@ -3769,90 +3900,96 @@
         <v>0</v>
       </c>
       <c r="AP23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ23" t="n">
         <v>0</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS23" t="n">
         <v>0</v>
       </c>
       <c r="AT23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV23" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="A24" s="1" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="n">
+        <v>22</v>
+      </c>
+      <c r="C24" t="inlineStr">
         <is>
           <t>res50_cifar10_layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B24" t="n">
+      <c r="D24" t="n">
         <v>256</v>
       </c>
-      <c r="C24" t="n">
+      <c r="E24" t="n">
         <v>1024</v>
       </c>
-      <c r="D24" t="n">
+      <c r="F24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
-        <v>1</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
       <c r="G24" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="n">
         <v>0.9992207359226744</v>
       </c>
-      <c r="H24" t="n">
+      <c r="J24" t="n">
         <v>0.0007768036068771</v>
       </c>
-      <c r="I24" t="n">
+      <c r="K24" t="n">
         <v>2.447408904054284e-06</v>
       </c>
-      <c r="J24" t="n">
+      <c r="L24" t="n">
         <v>0.0048509614599044</v>
       </c>
-      <c r="K24" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" t="n">
-        <v>0</v>
-      </c>
       <c r="M24" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
         <v>0.0102126734741113</v>
       </c>
-      <c r="N24" t="n">
+      <c r="P24" t="n">
         <v>2.266998570159042e-06</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>1.593831060306471e-07</v>
       </c>
-      <c r="P24" t="n">
+      <c r="R24" t="n">
         <v>0.8766321896041864</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="S24" t="n">
         <v>0.1055513241323831</v>
       </c>
-      <c r="R24" t="n">
+      <c r="T24" t="n">
         <v>4.544356477098394e-06</v>
       </c>
-      <c r="S24" t="n">
+      <c r="U24" t="n">
         <v>0.0027441444413706</v>
       </c>
-      <c r="T24" t="n">
+      <c r="V24" t="n">
         <v>1.723088346270953e-06</v>
       </c>
-      <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>1</v>
-      </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
@@ -3863,10 +4000,10 @@
         <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB24" t="n">
         <v>0</v>
@@ -3878,19 +4015,19 @@
         <v>0</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF24" t="n">
         <v>0</v>
       </c>
       <c r="AG24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH24" t="n">
         <v>0</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ24" t="n">
         <v>0</v>
@@ -3902,99 +4039,105 @@
         <v>0</v>
       </c>
       <c r="AM24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN24" t="n">
         <v>0</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP24" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ24" t="n">
         <v>0</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS24" t="n">
         <v>0</v>
       </c>
       <c r="AT24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV24" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="A25" s="1" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="n">
+        <v>23</v>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>res50_cifar10_layer4.1.conv3</t>
         </is>
       </c>
-      <c r="B25" t="n">
+      <c r="D25" t="n">
         <v>512</v>
       </c>
-      <c r="C25" t="n">
+      <c r="E25" t="n">
         <v>2048</v>
       </c>
-      <c r="D25" t="n">
+      <c r="F25" t="n">
         <v>4</v>
       </c>
-      <c r="E25" t="n">
-        <v>1</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
       <c r="G25" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" t="n">
         <v>0.9995911557656204</v>
       </c>
-      <c r="H25" t="n">
+      <c r="J25" t="n">
         <v>0.0004065229396586</v>
       </c>
-      <c r="I25" t="n">
+      <c r="K25" t="n">
         <v>2.308233176546458e-06</v>
       </c>
-      <c r="J25" t="n">
+      <c r="L25" t="n">
         <v>0.001252052380788</v>
       </c>
-      <c r="K25" t="n">
+      <c r="M25" t="n">
         <v>0.0022045009308685</v>
       </c>
-      <c r="L25" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" t="n">
         <v>0.0085893190158122</v>
       </c>
-      <c r="N25" t="n">
+      <c r="P25" t="n">
         <v>6.65603853542515e-06</v>
       </c>
-      <c r="O25" t="n">
+      <c r="Q25" t="n">
         <v>2.6719809029612e-09</v>
       </c>
-      <c r="P25" t="n">
+      <c r="R25" t="n">
         <v>0.9019072862842394</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="S25" t="n">
         <v>0.08431022925665239</v>
       </c>
-      <c r="R25" t="n">
+      <c r="T25" t="n">
         <v>0.0002540827897237</v>
       </c>
-      <c r="S25" t="n">
+      <c r="U25" t="n">
         <v>0.000736933320248</v>
       </c>
-      <c r="T25" t="n">
+      <c r="V25" t="n">
         <v>0.0007389242496067</v>
       </c>
-      <c r="U25" t="n">
-        <v>0</v>
-      </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
       <c r="W25" t="n">
         <v>0</v>
       </c>
@@ -4005,10 +4148,10 @@
         <v>0</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB25" t="n">
         <v>0</v>
@@ -4020,25 +4163,25 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF25" t="n">
         <v>0</v>
       </c>
       <c r="AG25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH25" t="n">
         <v>0</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ25" t="n">
         <v>0</v>
       </c>
       <c r="AK25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AL25" t="n">
         <v>0</v>
@@ -4050,93 +4193,99 @@
         <v>0</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV25" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="A26" s="1" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="n">
+        <v>24</v>
+      </c>
+      <c r="C26" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.11</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="D26" t="n">
         <v>256</v>
       </c>
-      <c r="C26" t="n">
+      <c r="E26" t="n">
         <v>512</v>
       </c>
-      <c r="D26" t="n">
+      <c r="F26" t="n">
         <v>16</v>
       </c>
-      <c r="E26" t="n">
+      <c r="G26" t="n">
         <v>3</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
+        <v>1</v>
+      </c>
+      <c r="I26" t="n">
         <v>0.9996680678072124</v>
       </c>
-      <c r="H26" t="n">
+      <c r="J26" t="n">
         <v>0.0003310160111192</v>
       </c>
-      <c r="I26" t="n">
+      <c r="K26" t="n">
         <v>9.031201238278807e-07</v>
       </c>
-      <c r="J26" t="n">
+      <c r="L26" t="n">
         <v>0.0018506265163714</v>
       </c>
-      <c r="K26" t="n">
+      <c r="M26" t="n">
         <v>0.0005293983839135</v>
       </c>
-      <c r="L26" t="n">
+      <c r="N26" t="n">
         <v>0.013241272499957</v>
       </c>
-      <c r="M26" t="n">
+      <c r="O26" t="n">
         <v>0.0060679864140775</v>
       </c>
-      <c r="N26" t="n">
+      <c r="P26" t="n">
         <v>0.0243645941542145</v>
       </c>
-      <c r="O26" t="n">
+      <c r="Q26" t="n">
         <v>0.0243493621704181</v>
       </c>
-      <c r="P26" t="n">
+      <c r="R26" t="n">
         <v>0.9253363049463504</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="S26" t="n">
         <v>3.924499493334557e-05</v>
       </c>
-      <c r="R26" t="n">
+      <c r="T26" t="n">
         <v>2.683152581244415e-06</v>
       </c>
-      <c r="S26" t="n">
+      <c r="U26" t="n">
         <v>0.0013186779217129</v>
       </c>
-      <c r="T26" t="n">
+      <c r="V26" t="n">
         <v>0.0028998089264526</v>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>1</v>
-      </c>
       <c r="W26" t="n">
         <v>0</v>
       </c>
@@ -4147,10 +4296,10 @@
         <v>0</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB26" t="n">
         <v>0</v>
@@ -4162,123 +4311,129 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF26" t="n">
         <v>0</v>
       </c>
       <c r="AG26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH26" t="n">
         <v>0</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ26" t="n">
         <v>0</v>
       </c>
       <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
         <v>0.9986721877849712</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AN26" t="n">
         <v>0.0013278122150287</v>
       </c>
-      <c r="AM26" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS26" t="n">
         <v>0.1112288009541753</v>
       </c>
-      <c r="AR26" t="n">
+      <c r="AT26" t="n">
         <v>0.8887711990458247</v>
       </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="A27" s="1" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="n">
+        <v>25</v>
+      </c>
+      <c r="C27" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.3</t>
         </is>
       </c>
-      <c r="B27" t="n">
+      <c r="D27" t="n">
         <v>64</v>
       </c>
-      <c r="C27" t="n">
+      <c r="E27" t="n">
         <v>128</v>
       </c>
-      <c r="D27" t="n">
+      <c r="F27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" t="n">
+      <c r="G27" t="n">
         <v>3</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
+        <v>1</v>
+      </c>
+      <c r="I27" t="n">
         <v>0.99888207517877</v>
       </c>
-      <c r="H27" t="n">
+      <c r="J27" t="n">
         <v>0.0011159215890448</v>
       </c>
-      <c r="I27" t="n">
+      <c r="K27" t="n">
         <v>1.990170640839141e-06</v>
       </c>
-      <c r="J27" t="n">
+      <c r="L27" t="n">
         <v>0.0477676752063472</v>
       </c>
-      <c r="K27" t="n">
+      <c r="M27" t="n">
         <v>0.8471142323602379</v>
       </c>
-      <c r="L27" t="n">
+      <c r="N27" t="n">
         <v>0.0453408193484484</v>
       </c>
-      <c r="M27" t="n">
+      <c r="O27" t="n">
         <v>0.0105882876871841</v>
       </c>
-      <c r="N27" t="n">
+      <c r="P27" t="n">
         <v>0.026454128008921</v>
       </c>
-      <c r="O27" t="n">
+      <c r="Q27" t="n">
         <v>0.0113348182092279</v>
       </c>
-      <c r="P27" t="n">
+      <c r="R27" t="n">
         <v>2.836818900331346e-06</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="S27" t="n">
         <v>0.011390273669404</v>
       </c>
-      <c r="R27" t="n">
+      <c r="T27" t="n">
         <v>2.284223754887909e-06</v>
       </c>
-      <c r="S27" t="n">
+      <c r="U27" t="n">
         <v>3.732367462237458e-06</v>
       </c>
-      <c r="T27" t="n">
+      <c r="V27" t="n">
         <v>8.949002562325439e-07</v>
       </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>1</v>
-      </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
@@ -4289,10 +4444,10 @@
         <v>0</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB27" t="n">
         <v>0</v>
@@ -4304,19 +4459,19 @@
         <v>0</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF27" t="n">
         <v>0</v>
       </c>
       <c r="AG27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH27" t="n">
         <v>0</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ27" t="n">
         <v>0</v>
@@ -4325,102 +4480,108 @@
         <v>0</v>
       </c>
       <c r="AL27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP27" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS27" t="n">
         <v>0.1111784692725899</v>
       </c>
-      <c r="AR27" t="n">
+      <c r="AT27" t="n">
         <v>0.88882153072741</v>
       </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="A28" s="1" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="n">
+        <v>26</v>
+      </c>
+      <c r="C28" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.6</t>
         </is>
       </c>
-      <c r="B28" t="n">
+      <c r="D28" t="n">
         <v>128</v>
       </c>
-      <c r="C28" t="n">
+      <c r="E28" t="n">
         <v>256</v>
       </c>
-      <c r="D28" t="n">
+      <c r="F28" t="n">
         <v>2</v>
       </c>
-      <c r="E28" t="n">
+      <c r="G28" t="n">
         <v>3</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
         <v>0.99942515141177</v>
       </c>
-      <c r="H28" t="n">
+      <c r="J28" t="n">
         <v>0.0005727496680335</v>
       </c>
-      <c r="I28" t="n">
+      <c r="K28" t="n">
         <v>2.085858652156289e-06</v>
       </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>0.0002631834033581</v>
       </c>
-      <c r="K28" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
         <v>0.0639158984032379</v>
       </c>
-      <c r="M28" t="n">
+      <c r="O28" t="n">
         <v>0.005697673005963</v>
       </c>
-      <c r="N28" t="n">
+      <c r="P28" t="n">
         <v>0.009139840990158901</v>
       </c>
-      <c r="O28" t="n">
+      <c r="Q28" t="n">
         <v>0.0273924128605446</v>
       </c>
-      <c r="P28" t="n">
+      <c r="R28" t="n">
         <v>0.8766614655759281</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="S28" t="n">
         <v>0.009162509664844699</v>
       </c>
-      <c r="R28" t="n">
+      <c r="T28" t="n">
         <v>0.0002591519364518</v>
       </c>
-      <c r="S28" t="n">
+      <c r="U28" t="n">
         <v>0.0069888453529121</v>
       </c>
-      <c r="T28" t="n">
+      <c r="V28" t="n">
         <v>0.0005189984122594</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>1</v>
-      </c>
       <c r="W28" t="n">
         <v>0</v>
       </c>
@@ -4431,10 +4592,10 @@
         <v>0</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB28" t="n">
         <v>0</v>
@@ -4446,40 +4607,40 @@
         <v>0</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF28" t="n">
         <v>0</v>
       </c>
       <c r="AG28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH28" t="n">
         <v>0</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ28" t="n">
         <v>0</v>
       </c>
       <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
         <v>0.6389108539205585</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AN28" t="n">
         <v>0.3610891460794415</v>
       </c>
-      <c r="AM28" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ28" t="n">
         <v>0</v>
@@ -4491,78 +4652,84 @@
         <v>0</v>
       </c>
       <c r="AT28" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="A29" s="1" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="n">
+        <v>27</v>
+      </c>
+      <c r="C29" t="inlineStr">
         <is>
           <t>vgg11_cifar10_features.8</t>
         </is>
       </c>
-      <c r="B29" t="n">
+      <c r="D29" t="n">
         <v>256</v>
       </c>
-      <c r="C29" t="n">
+      <c r="E29" t="n">
         <v>256</v>
       </c>
-      <c r="D29" t="n">
+      <c r="F29" t="n">
         <v>2</v>
       </c>
-      <c r="E29" t="n">
+      <c r="G29" t="n">
         <v>3</v>
       </c>
-      <c r="F29" t="n">
-        <v>1</v>
-      </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
         <v>0.9989024572327546</v>
       </c>
-      <c r="H29" t="n">
+      <c r="J29" t="n">
         <v>0.0010954443325015</v>
       </c>
-      <c r="I29" t="n">
+      <c r="K29" t="n">
         <v>2.085373199513703e-06</v>
       </c>
-      <c r="J29" t="n">
+      <c r="L29" t="n">
         <v>0.0003249499030717</v>
       </c>
-      <c r="K29" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
         <v>0.0626113101521959</v>
       </c>
-      <c r="M29" t="n">
+      <c r="O29" t="n">
         <v>0.0105005848623142</v>
       </c>
-      <c r="N29" t="n">
+      <c r="P29" t="n">
         <v>0.0260956513652585</v>
       </c>
-      <c r="O29" t="n">
+      <c r="Q29" t="n">
         <v>0.0208772974418185</v>
       </c>
-      <c r="P29" t="n">
+      <c r="R29" t="n">
         <v>0.876651605047122</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="S29" t="n">
         <v>2.223139523310739e-05</v>
       </c>
-      <c r="R29" t="n">
+      <c r="T29" t="n">
         <v>0.0006374418382647</v>
       </c>
-      <c r="S29" t="n">
+      <c r="U29" t="n">
         <v>0.0012017257536252</v>
       </c>
-      <c r="T29" t="n">
+      <c r="V29" t="n">
         <v>0.0010771625572955</v>
       </c>
-      <c r="U29" t="n">
-        <v>0</v>
-      </c>
-      <c r="V29" t="n">
-        <v>1</v>
-      </c>
       <c r="W29" t="n">
         <v>0</v>
       </c>
@@ -4573,10 +4740,10 @@
         <v>0</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB29" t="n">
         <v>0</v>
@@ -4588,40 +4755,40 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF29" t="n">
         <v>0</v>
       </c>
       <c r="AG29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH29" t="n">
         <v>0</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ29" t="n">
         <v>0</v>
       </c>
       <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
         <v>0.9985238453035939</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AN29" t="n">
         <v>0.0014761546964058</v>
       </c>
-      <c r="AM29" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>0</v>
-      </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ29" t="n">
         <v>0</v>
@@ -4633,69 +4800,75 @@
         <v>0</v>
       </c>
       <c r="AT29" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="A30" s="1" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="n">
+        <v>28</v>
+      </c>
+      <c r="C30" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.0.conv1</t>
         </is>
       </c>
-      <c r="B30" t="n">
+      <c r="D30" t="n">
         <v>256</v>
       </c>
-      <c r="C30" t="n">
+      <c r="E30" t="n">
         <v>128</v>
       </c>
-      <c r="D30" t="n">
+      <c r="F30" t="n">
         <v>32</v>
       </c>
-      <c r="E30" t="n">
-        <v>1</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
       <c r="G30" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
         <v>0.687915780911081</v>
       </c>
-      <c r="H30" t="n">
+      <c r="J30" t="n">
         <v>0.3120818685540765</v>
       </c>
-      <c r="I30" t="n">
+      <c r="K30" t="n">
         <v>2.337473298073471e-06</v>
       </c>
-      <c r="J30" t="n">
+      <c r="L30" t="n">
         <v>0.0004864291922182</v>
       </c>
-      <c r="K30" t="n">
+      <c r="M30" t="n">
         <v>0.998525965030692</v>
       </c>
-      <c r="L30" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" t="n">
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
         <v>1.520115387407094e-05</v>
       </c>
-      <c r="N30" t="n">
+      <c r="P30" t="n">
         <v>6.5772260339373e-07</v>
       </c>
-      <c r="O30" t="n">
-        <v>0</v>
-      </c>
-      <c r="P30" t="n">
+      <c r="Q30" t="n">
+        <v>0</v>
+      </c>
+      <c r="R30" t="n">
         <v>4.690917161568602e-09</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="S30" t="n">
         <v>0.0009717291481507</v>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="n">
-        <v>0</v>
-      </c>
       <c r="T30" t="n">
         <v>0</v>
       </c>
@@ -4703,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
         <v>0</v>
@@ -4715,10 +4888,10 @@
         <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
         <v>0</v>
@@ -4730,7 +4903,7 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF30" t="n">
         <v>0</v>
@@ -4763,89 +4936,95 @@
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ30" t="n">
         <v>0</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS30" t="n">
         <v>0</v>
       </c>
       <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="A31" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="n">
+        <v>29</v>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer2.3.conv3</t>
         </is>
       </c>
-      <c r="B31" t="n">
+      <c r="D31" t="n">
         <v>128</v>
       </c>
-      <c r="C31" t="n">
+      <c r="E31" t="n">
         <v>512</v>
       </c>
-      <c r="D31" t="n">
+      <c r="F31" t="n">
         <v>16</v>
       </c>
-      <c r="E31" t="n">
-        <v>1</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
       <c r="G31" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
         <v>0.998510113816204</v>
       </c>
-      <c r="H31" t="n">
+      <c r="J31" t="n">
         <v>0.0014876800660199</v>
       </c>
-      <c r="I31" t="n">
+      <c r="K31" t="n">
         <v>2.193056231599883e-06</v>
       </c>
-      <c r="J31" t="n">
+      <c r="L31" t="n">
         <v>1.47890763001068e-06</v>
       </c>
-      <c r="K31" t="n">
+      <c r="M31" t="n">
         <v>0.9012230225579868</v>
       </c>
-      <c r="L31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" t="n">
+      <c r="N31" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" t="n">
         <v>0.0027675886738829</v>
       </c>
-      <c r="N31" t="n">
+      <c r="P31" t="n">
         <v>3.618109221851631e-05</v>
       </c>
-      <c r="O31" t="n">
-        <v>0</v>
-      </c>
-      <c r="P31" t="n">
+      <c r="Q31" t="n">
+        <v>0</v>
+      </c>
+      <c r="R31" t="n">
         <v>6.589654570662431e-06</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="S31" t="n">
         <v>0.0959633469220855</v>
       </c>
-      <c r="R31" t="n">
+      <c r="T31" t="n">
         <v>1.183577723508598e-06</v>
       </c>
-      <c r="S31" t="n">
+      <c r="U31" t="n">
         <v>5.955523575880909e-07</v>
       </c>
-      <c r="T31" t="n">
-        <v>0</v>
-      </c>
-      <c r="U31" t="n">
-        <v>0</v>
-      </c>
       <c r="V31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W31" t="n">
         <v>0</v>
@@ -4857,10 +5036,10 @@
         <v>0</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB31" t="n">
         <v>0</v>
@@ -4872,19 +5051,19 @@
         <v>0</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF31" t="n">
         <v>0</v>
       </c>
       <c r="AG31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH31" t="n">
         <v>0</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ31" t="n">
         <v>0</v>
@@ -4896,98 +5075,104 @@
         <v>0</v>
       </c>
       <c r="AM31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN31" t="n">
         <v>0</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP31" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ31" t="n">
         <v>0</v>
       </c>
       <c r="AR31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS31" t="n">
         <v>0</v>
       </c>
       <c r="AT31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV31" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="A32" s="1" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="n">
+        <v>30</v>
+      </c>
+      <c r="C32" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.0.conv3</t>
         </is>
       </c>
-      <c r="B32" t="n">
+      <c r="D32" t="n">
         <v>256</v>
       </c>
-      <c r="C32" t="n">
+      <c r="E32" t="n">
         <v>1024</v>
       </c>
-      <c r="D32" t="n">
+      <c r="F32" t="n">
         <v>16</v>
       </c>
-      <c r="E32" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
       <c r="G32" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" t="n">
         <v>0.9960449587225144</v>
       </c>
-      <c r="H32" t="n">
+      <c r="J32" t="n">
         <v>0.0039526775500007</v>
       </c>
-      <c r="I32" t="n">
+      <c r="K32" t="n">
         <v>2.350665940565848e-06</v>
       </c>
-      <c r="J32" t="n">
+      <c r="L32" t="n">
         <v>5.946874348767533e-06</v>
       </c>
-      <c r="K32" t="n">
+      <c r="M32" t="n">
         <v>0.8811868742363759</v>
       </c>
-      <c r="L32" t="n">
+      <c r="N32" t="n">
         <v>1.34280672929432e-08</v>
       </c>
-      <c r="M32" t="n">
+      <c r="O32" t="n">
         <v>0.0091541084786259</v>
       </c>
-      <c r="N32" t="n">
+      <c r="P32" t="n">
         <v>3.645308440886898e-05</v>
       </c>
-      <c r="O32" t="n">
-        <v>0</v>
-      </c>
-      <c r="P32" t="n">
+      <c r="Q32" t="n">
+        <v>0</v>
+      </c>
+      <c r="R32" t="n">
         <v>5.494425942541084e-06</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="S32" t="n">
         <v>0.1096088240436533</v>
       </c>
-      <c r="R32" t="n">
+      <c r="T32" t="n">
         <v>1.417453817469466e-06</v>
       </c>
-      <c r="S32" t="n">
+      <c r="U32" t="n">
         <v>8.549132155655589e-07</v>
       </c>
-      <c r="T32" t="n">
-        <v>0</v>
-      </c>
-      <c r="U32" t="n">
-        <v>0</v>
-      </c>
       <c r="V32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32" t="n">
         <v>0</v>
@@ -4999,16 +5184,16 @@
         <v>0</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB32" t="n">
         <v>0</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD32" t="n">
         <v>0</v>
@@ -5020,13 +5205,13 @@
         <v>0</v>
       </c>
       <c r="AG32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH32" t="n">
         <v>0</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ32" t="n">
         <v>0</v>
@@ -5038,16 +5223,16 @@
         <v>0</v>
       </c>
       <c r="AM32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN32" t="n">
         <v>0</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ32" t="n">
         <v>0</v>
@@ -5059,77 +5244,83 @@
         <v>0</v>
       </c>
       <c r="AT32" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV32" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+      <c r="A33" s="1" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="n">
+        <v>31</v>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer3.1.conv2</t>
         </is>
       </c>
-      <c r="B33" t="n">
+      <c r="D33" t="n">
         <v>256</v>
       </c>
-      <c r="C33" t="n">
+      <c r="E33" t="n">
         <v>256</v>
       </c>
-      <c r="D33" t="n">
+      <c r="F33" t="n">
         <v>16</v>
       </c>
-      <c r="E33" t="n">
+      <c r="G33" t="n">
         <v>3</v>
       </c>
-      <c r="F33" t="n">
+      <c r="H33" t="n">
         <v>2</v>
       </c>
-      <c r="G33" t="n">
+      <c r="I33" t="n">
         <v>0.995515427360008</v>
       </c>
-      <c r="H33" t="n">
+      <c r="J33" t="n">
         <v>0.0044825269896488</v>
       </c>
-      <c r="I33" t="n">
+      <c r="K33" t="n">
         <v>2.032588798720574e-06</v>
       </c>
-      <c r="J33" t="n">
+      <c r="L33" t="n">
         <v>9.588710215712296e-07</v>
       </c>
-      <c r="K33" t="n">
+      <c r="M33" t="n">
         <v>0.8808357307180521</v>
       </c>
-      <c r="L33" t="n">
+      <c r="N33" t="n">
         <v>3.747570245810775e-06</v>
       </c>
-      <c r="M33" t="n">
+      <c r="O33" t="n">
         <v>0.0137184750261219</v>
       </c>
-      <c r="N33" t="n">
+      <c r="P33" t="n">
         <v>0.1053910213702244</v>
       </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="n">
         <v>6.682667512189507e-06</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="S33" t="n">
         <v>3.857281687835234e-05</v>
       </c>
-      <c r="R33" t="n">
+      <c r="T33" t="n">
         <v>2.556989390856627e-06</v>
       </c>
-      <c r="S33" t="n">
+      <c r="U33" t="n">
         <v>2.240909008289876e-06</v>
       </c>
-      <c r="T33" t="n">
-        <v>0</v>
-      </c>
-      <c r="U33" t="n">
-        <v>0</v>
-      </c>
       <c r="V33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W33" t="n">
         <v>0</v>
@@ -5141,16 +5332,16 @@
         <v>0</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB33" t="n">
         <v>0</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD33" t="n">
         <v>0</v>
@@ -5162,13 +5353,13 @@
         <v>0</v>
       </c>
       <c r="AG33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH33" t="n">
         <v>0</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ33" t="n">
         <v>0</v>
@@ -5189,89 +5380,95 @@
         <v>0</v>
       </c>
       <c r="AP33" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR33" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS33" t="n">
         <v>0.0006973143144272</v>
       </c>
-      <c r="AR33" t="n">
+      <c r="AT33" t="n">
         <v>0.9993026856855728</v>
       </c>
-      <c r="AS33" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT33" t="n">
+      <c r="AU33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV33" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="inlineStr">
+      <c r="A34" s="1" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" t="n">
+        <v>32</v>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>deeplabv3_oxfordpet_backbone.layer4.0.conv2</t>
         </is>
       </c>
-      <c r="B34" t="n">
+      <c r="D34" t="n">
         <v>512</v>
       </c>
-      <c r="C34" t="n">
+      <c r="E34" t="n">
         <v>512</v>
       </c>
-      <c r="D34" t="n">
+      <c r="F34" t="n">
         <v>16</v>
       </c>
-      <c r="E34" t="n">
+      <c r="G34" t="n">
         <v>3</v>
       </c>
-      <c r="F34" t="n">
+      <c r="H34" t="n">
         <v>2</v>
       </c>
-      <c r="G34" t="n">
+      <c r="I34" t="n">
         <v>0.585715613474575</v>
       </c>
-      <c r="H34" t="n">
+      <c r="J34" t="n">
         <v>0.4142826077704672</v>
       </c>
-      <c r="I34" t="n">
+      <c r="K34" t="n">
         <v>1.765693413535188e-06</v>
       </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
+      <c r="L34" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" t="n">
         <v>0.9995103929426736</v>
       </c>
-      <c r="L34" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" t="n">
+      <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="n">
         <v>0.0002043602390279</v>
       </c>
-      <c r="N34" t="n">
+      <c r="P34" t="n">
         <v>0.0002797632133216</v>
       </c>
-      <c r="O34" t="n">
-        <v>0</v>
-      </c>
-      <c r="P34" t="n">
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="R34" t="n">
         <v>4.272481738098341e-07</v>
       </c>
-      <c r="Q34" t="n">
+      <c r="S34" t="n">
         <v>4.944929559690208e-06</v>
       </c>
-      <c r="R34" t="n">
+      <c r="T34" t="n">
         <v>9.836569873780676e-08</v>
       </c>
-      <c r="S34" t="n">
-        <v>0</v>
-      </c>
-      <c r="T34" t="n">
-        <v>0</v>
-      </c>
       <c r="U34" t="n">
         <v>0</v>
       </c>
       <c r="V34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W34" t="n">
         <v>0</v>
@@ -5283,16 +5480,16 @@
         <v>0</v>
       </c>
       <c r="Z34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB34" t="n">
         <v>0</v>
       </c>
       <c r="AC34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD34" t="n">
         <v>0</v>
@@ -5322,99 +5519,105 @@
         <v>0</v>
       </c>
       <c r="AM34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN34" t="n">
         <v>0</v>
       </c>
       <c r="AO34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ34" t="n">
         <v>0</v>
       </c>
       <c r="AR34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS34" t="n">
         <v>0</v>
       </c>
       <c r="AT34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV34" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="inlineStr">
+      <c r="A35" s="1" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" t="n">
+        <v>33</v>
+      </c>
+      <c r="C35" t="inlineStr">
         <is>
           <t>merge0</t>
         </is>
       </c>
-      <c r="B35" t="n">
+      <c r="D35" t="n">
         <v>3</v>
       </c>
-      <c r="C35" t="n">
+      <c r="E35" t="n">
         <v>64</v>
       </c>
-      <c r="D35" t="n">
+      <c r="F35" t="n">
         <v>32</v>
       </c>
-      <c r="E35" t="n">
+      <c r="G35" t="n">
         <v>3</v>
       </c>
-      <c r="F35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
+        <v>1</v>
+      </c>
+      <c r="I35" t="n">
         <v>0.9994521224065214</v>
       </c>
-      <c r="H35" t="n">
+      <c r="J35" t="n">
         <v>0.0005458481057323</v>
       </c>
-      <c r="I35" t="n">
+      <c r="K35" t="n">
         <v>2.016426201907922e-06</v>
       </c>
-      <c r="J35" t="n">
+      <c r="L35" t="n">
         <v>0.1449986133428514</v>
       </c>
-      <c r="K35" t="n">
+      <c r="M35" t="n">
         <v>0.7726846021545537</v>
       </c>
-      <c r="L35" t="n">
+      <c r="N35" t="n">
         <v>0.02922175082935145</v>
       </c>
-      <c r="M35" t="n">
+      <c r="O35" t="n">
         <v>0.001265662129374428</v>
       </c>
-      <c r="N35" t="n">
+      <c r="P35" t="n">
         <v>0.02983793155150225</v>
       </c>
-      <c r="O35" t="n">
+      <c r="Q35" t="n">
         <v>0.00547850702328185</v>
       </c>
-      <c r="P35" t="n">
+      <c r="R35" t="n">
         <v>1.789222437131307e-06</v>
       </c>
-      <c r="Q35" t="n">
+      <c r="S35" t="n">
         <v>0.01650818311379609</v>
       </c>
-      <c r="R35" t="n">
+      <c r="T35" t="n">
         <v>5.010551673225345e-07</v>
       </c>
-      <c r="S35" t="n">
+      <c r="U35" t="n">
         <v>2.209025093086417e-06</v>
       </c>
-      <c r="T35" t="n">
+      <c r="V35" t="n">
         <v>2.192191595980413e-07</v>
       </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>1</v>
-      </c>
       <c r="W35" t="n">
         <v>0</v>
       </c>
@@ -5425,16 +5628,16 @@
         <v>0</v>
       </c>
       <c r="Z35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB35" t="n">
         <v>0</v>
       </c>
       <c r="AC35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD35" t="n">
         <v>0</v>
@@ -5446,13 +5649,13 @@
         <v>0</v>
       </c>
       <c r="AG35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH35" t="n">
         <v>0</v>
       </c>
       <c r="AI35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ35" t="n">
         <v>0</v>
@@ -5461,102 +5664,108 @@
         <v>0</v>
       </c>
       <c r="AL35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS35" t="n">
         <v>0.1115481423019123</v>
       </c>
-      <c r="AR35" t="n">
+      <c r="AT35" t="n">
         <v>0.8884518576980875</v>
       </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="inlineStr">
+      <c r="A36" s="1" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" t="n">
+        <v>34</v>
+      </c>
+      <c r="C36" t="inlineStr">
         <is>
           <t>merge1</t>
         </is>
       </c>
-      <c r="B36" t="n">
+      <c r="D36" t="n">
         <v>64</v>
       </c>
-      <c r="C36" t="n">
+      <c r="E36" t="n">
         <v>64</v>
       </c>
-      <c r="D36" t="n">
+      <c r="F36" t="n">
         <v>32</v>
       </c>
-      <c r="E36" t="n">
+      <c r="G36" t="n">
         <v>3</v>
       </c>
-      <c r="F36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
+        <v>1</v>
+      </c>
+      <c r="I36" t="n">
         <v>0.9958791751886233</v>
       </c>
-      <c r="H36" t="n">
+      <c r="J36" t="n">
         <v>0.0041189649497534</v>
       </c>
-      <c r="I36" t="n">
+      <c r="K36" t="n">
         <v>1.8468000788543e-06</v>
       </c>
-      <c r="J36" t="n">
+      <c r="L36" t="n">
         <v>0.0679886006995979</v>
       </c>
-      <c r="K36" t="n">
+      <c r="M36" t="n">
         <v>0.817946384542817</v>
       </c>
-      <c r="L36" t="n">
+      <c r="N36" t="n">
         <v>0.08478842279106345</v>
       </c>
-      <c r="M36" t="n">
+      <c r="O36" t="n">
         <v>0.007999330535035949</v>
       </c>
-      <c r="N36" t="n">
+      <c r="P36" t="n">
         <v>0.01322887980723165</v>
       </c>
-      <c r="O36" t="n">
+      <c r="Q36" t="n">
         <v>0.003913283265981179</v>
       </c>
-      <c r="P36" t="n">
+      <c r="R36" t="n">
         <v>1.40709466575123e-06</v>
       </c>
-      <c r="Q36" t="n">
+      <c r="S36" t="n">
         <v>0.00230602559346735</v>
       </c>
-      <c r="R36" t="n">
+      <c r="T36" t="n">
         <v>2.463352824609093e-07</v>
       </c>
-      <c r="S36" t="n">
+      <c r="U36" t="n">
         <v>6.543829930075365e-07</v>
       </c>
-      <c r="T36" t="n">
+      <c r="V36" t="n">
         <v>0.001826750180833314</v>
       </c>
-      <c r="U36" t="n">
-        <v>0</v>
-      </c>
-      <c r="V36" t="n">
-        <v>1</v>
-      </c>
       <c r="W36" t="n">
         <v>0</v>
       </c>
@@ -5567,34 +5776,34 @@
         <v>0</v>
       </c>
       <c r="Z36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB36" t="n">
         <v>0</v>
       </c>
       <c r="AC36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="n">
-        <v>0</v>
-      </c>
       <c r="AF36" t="n">
         <v>0</v>
       </c>
       <c r="AG36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH36" t="n">
         <v>0</v>
       </c>
       <c r="AI36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ36" t="n">
         <v>0</v>
@@ -5603,102 +5812,108 @@
         <v>0</v>
       </c>
       <c r="AL36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO36" t="n">
         <v>0.5</v>
       </c>
-      <c r="AN36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO36" t="n">
-        <v>0</v>
-      </c>
       <c r="AP36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR36" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS36" t="n">
         <v>4.045684717463313e-05</v>
       </c>
-      <c r="AR36" t="n">
+      <c r="AT36" t="n">
         <v>0.9999595431528253</v>
       </c>
-      <c r="AS36" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="n">
+      <c r="AU36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV36" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="inlineStr">
+      <c r="A37" s="1" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" t="n">
+        <v>35</v>
+      </c>
+      <c r="C37" t="inlineStr">
         <is>
           <t>merge2</t>
         </is>
       </c>
-      <c r="B37" t="n">
+      <c r="D37" t="n">
         <v>128</v>
       </c>
-      <c r="C37" t="n">
+      <c r="E37" t="n">
         <v>128</v>
       </c>
-      <c r="D37" t="n">
+      <c r="F37" t="n">
         <v>16</v>
       </c>
-      <c r="E37" t="n">
+      <c r="G37" t="n">
         <v>3</v>
       </c>
-      <c r="F37" t="n">
-        <v>1</v>
-      </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
+        <v>1</v>
+      </c>
+      <c r="I37" t="n">
         <v>0.9974987302026275</v>
       </c>
-      <c r="H37" t="n">
+      <c r="J37" t="n">
         <v>0.0024994083891999</v>
       </c>
-      <c r="I37" t="n">
+      <c r="K37" t="n">
         <v>1.84834662819737e-06</v>
       </c>
-      <c r="J37" t="n">
+      <c r="L37" t="n">
         <v>0.04885443782451615</v>
       </c>
-      <c r="K37" t="n">
+      <c r="M37" t="n">
         <v>0.8464321916283952</v>
       </c>
-      <c r="L37" t="n">
+      <c r="N37" t="n">
         <v>0.0626124150869414</v>
       </c>
-      <c r="M37" t="n">
+      <c r="O37" t="n">
         <v>0.01153383191101295</v>
       </c>
-      <c r="N37" t="n">
+      <c r="P37" t="n">
         <v>0.01468491649314149</v>
       </c>
-      <c r="O37" t="n">
+      <c r="Q37" t="n">
         <v>0.009783054805645751</v>
       </c>
-      <c r="P37" t="n">
+      <c r="R37" t="n">
         <v>5.733043740622462e-06</v>
       </c>
-      <c r="Q37" t="n">
+      <c r="S37" t="n">
         <v>0.00492664716961325</v>
       </c>
-      <c r="R37" t="n">
+      <c r="T37" t="n">
         <v>1.733031975860329e-06</v>
       </c>
-      <c r="S37" t="n">
+      <c r="U37" t="n">
         <v>1.10202147484146e-06</v>
       </c>
-      <c r="T37" t="n">
+      <c r="V37" t="n">
         <v>0.0001856175617355569</v>
       </c>
-      <c r="U37" t="n">
-        <v>0</v>
-      </c>
-      <c r="V37" t="n">
-        <v>1</v>
-      </c>
       <c r="W37" t="n">
         <v>0</v>
       </c>
@@ -5709,34 +5924,34 @@
         <v>0</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB37" t="n">
         <v>0</v>
       </c>
       <c r="AC37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="n">
-        <v>0</v>
-      </c>
       <c r="AF37" t="n">
         <v>0</v>
       </c>
       <c r="AG37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH37" t="n">
         <v>0</v>
       </c>
       <c r="AI37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ37" t="n">
         <v>0</v>
@@ -5745,102 +5960,108 @@
         <v>0</v>
       </c>
       <c r="AL37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR37" t="n">
+        <v>1</v>
+      </c>
+      <c r="AS37" t="n">
         <v>7.593186896218585e-07</v>
       </c>
-      <c r="AR37" t="n">
+      <c r="AT37" t="n">
         <v>0.9999992406813103</v>
       </c>
-      <c r="AS37" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="n">
+      <c r="AU37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV37" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="inlineStr">
+      <c r="A38" s="1" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" t="n">
+        <v>36</v>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>merge3</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="D38" t="n">
         <v>256</v>
       </c>
-      <c r="C38" t="n">
+      <c r="E38" t="n">
         <v>256</v>
       </c>
-      <c r="D38" t="n">
+      <c r="F38" t="n">
         <v>8</v>
       </c>
-      <c r="E38" t="n">
+      <c r="G38" t="n">
         <v>3</v>
       </c>
-      <c r="F38" t="n">
-        <v>1</v>
-      </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
+        <v>1</v>
+      </c>
+      <c r="I38" t="n">
         <v>0.9979990212574712</v>
       </c>
-      <c r="H38" t="n">
+      <c r="J38" t="n">
         <v>0.0019989391844899</v>
       </c>
-      <c r="I38" t="n">
+      <c r="K38" t="n">
         <v>2.026496494465474e-06</v>
       </c>
-      <c r="J38" t="n">
+      <c r="L38" t="n">
         <v>0.0003923447285396</v>
       </c>
-      <c r="K38" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" t="n">
+      <c r="M38" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" t="n">
         <v>0.04334823532396045</v>
       </c>
-      <c r="M38" t="n">
+      <c r="O38" t="n">
         <v>0.01144556469392555</v>
       </c>
-      <c r="N38" t="n">
+      <c r="P38" t="n">
         <v>0.0261969292005361</v>
       </c>
-      <c r="O38" t="n">
+      <c r="Q38" t="n">
         <v>0.01014550503560397</v>
       </c>
-      <c r="P38" t="n">
+      <c r="R38" t="n">
         <v>0.9015655972090482</v>
       </c>
-      <c r="Q38" t="n">
+      <c r="S38" t="n">
         <v>0.005003277677263867</v>
       </c>
-      <c r="R38" t="n">
+      <c r="T38" t="n">
         <v>9.906762082419887e-05</v>
       </c>
-      <c r="S38" t="n">
+      <c r="U38" t="n">
         <v>0.00169001890292675</v>
       </c>
-      <c r="T38" t="n">
+      <c r="V38" t="n">
         <v>0.0001134465458266892</v>
       </c>
-      <c r="U38" t="n">
-        <v>0</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1</v>
-      </c>
       <c r="W38" t="n">
         <v>0</v>
       </c>
@@ -5851,34 +6072,34 @@
         <v>0</v>
       </c>
       <c r="Z38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB38" t="n">
         <v>0</v>
       </c>
       <c r="AC38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="n">
         <v>0.5</v>
       </c>
-      <c r="AD38" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>0</v>
-      </c>
       <c r="AF38" t="n">
         <v>0</v>
       </c>
       <c r="AG38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH38" t="n">
         <v>0</v>
       </c>
       <c r="AI38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ38" t="n">
         <v>0</v>
@@ -5887,19 +6108,19 @@
         <v>0</v>
       </c>
       <c r="AL38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AM38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP38" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ38" t="n">
         <v>0</v>
@@ -5911,78 +6132,84 @@
         <v>0</v>
       </c>
       <c r="AT38" t="n">
+        <v>1</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV38" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="inlineStr">
+      <c r="A39" s="1" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" t="n">
+        <v>37</v>
+      </c>
+      <c r="C39" t="inlineStr">
         <is>
           <t>merge4</t>
         </is>
       </c>
-      <c r="B39" t="n">
+      <c r="D39" t="n">
         <v>512</v>
       </c>
-      <c r="C39" t="n">
+      <c r="E39" t="n">
         <v>512</v>
       </c>
-      <c r="D39" t="n">
+      <c r="F39" t="n">
         <v>4</v>
       </c>
-      <c r="E39" t="n">
+      <c r="G39" t="n">
         <v>3</v>
       </c>
-      <c r="F39" t="n">
-        <v>1</v>
-      </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
+        <v>1</v>
+      </c>
+      <c r="I39" t="n">
         <v>0.9984751852316146</v>
       </c>
-      <c r="H39" t="n">
+      <c r="J39" t="n">
         <v>0.001522732027290325</v>
       </c>
-      <c r="I39" t="n">
+      <c r="K39" t="n">
         <v>2.069679550679921e-06</v>
       </c>
-      <c r="J39" t="n">
+      <c r="L39" t="n">
         <v>0.004106583082919475</v>
       </c>
-      <c r="K39" t="n">
+      <c r="M39" t="n">
         <v>0.2474104136445792</v>
       </c>
-      <c r="L39" t="n">
+      <c r="N39" t="n">
         <v>0.008499819696778349</v>
       </c>
-      <c r="M39" t="n">
+      <c r="O39" t="n">
         <v>0.0051705747060144</v>
       </c>
-      <c r="N39" t="n">
+      <c r="P39" t="n">
         <v>0.0219258846782166</v>
       </c>
-      <c r="O39" t="n">
+      <c r="Q39" t="n">
         <v>0.01070886912061861</v>
       </c>
-      <c r="P39" t="n">
+      <c r="R39" t="n">
         <v>0.6985748931733691</v>
       </c>
-      <c r="Q39" t="n">
+      <c r="S39" t="n">
         <v>3.561994969369448e-05</v>
       </c>
-      <c r="R39" t="n">
+      <c r="T39" t="n">
         <v>0.00183273361053445</v>
       </c>
-      <c r="S39" t="n">
+      <c r="U39" t="n">
         <v>3.896423944595049e-05</v>
       </c>
-      <c r="T39" t="n">
+      <c r="V39" t="n">
         <v>0.00169562883644655</v>
       </c>
-      <c r="U39" t="n">
-        <v>0</v>
-      </c>
-      <c r="V39" t="n">
-        <v>1</v>
-      </c>
       <c r="W39" t="n">
         <v>0</v>
       </c>
@@ -5993,10 +6220,10 @@
         <v>0</v>
       </c>
       <c r="Z39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA39" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB39" t="n">
         <v>0</v>
@@ -6008,123 +6235,129 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF39" t="n">
         <v>0</v>
       </c>
       <c r="AG39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AH39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI39" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ39" t="n">
         <v>0</v>
       </c>
       <c r="AK39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM39" t="n">
         <v>0.7497834260088212</v>
       </c>
-      <c r="AL39" t="n">
+      <c r="AN39" t="n">
         <v>0.00021657399117865</v>
       </c>
-      <c r="AM39" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN39" t="n">
-        <v>0</v>
-      </c>
       <c r="AO39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR39" t="n">
         <v>0.75</v>
       </c>
-      <c r="AQ39" t="n">
+      <c r="AS39" t="n">
         <v>0.08335139364824007</v>
       </c>
-      <c r="AR39" t="n">
+      <c r="AT39" t="n">
         <v>0.6666486063517598</v>
       </c>
-      <c r="AS39" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT39" t="n">
+      <c r="AU39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV39" t="n">
         <v>1</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="inlineStr">
+      <c r="A40" s="1" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" t="n">
+        <v>38</v>
+      </c>
+      <c r="C40" t="inlineStr">
         <is>
           <t>merge5</t>
         </is>
       </c>
-      <c r="B40" t="n">
+      <c r="D40" t="n">
         <v>512</v>
       </c>
-      <c r="C40" t="n">
+      <c r="E40" t="n">
         <v>512</v>
       </c>
-      <c r="D40" t="n">
+      <c r="F40" t="n">
         <v>8</v>
       </c>
-      <c r="E40" t="n">
+      <c r="G40" t="n">
         <v>3</v>
       </c>
-      <c r="F40" t="n">
-        <v>1</v>
-      </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
+        <v>1</v>
+      </c>
+      <c r="I40" t="n">
         <v>0.99955099862434</v>
       </c>
-      <c r="H40" t="n">
+      <c r="J40" t="n">
         <v>0.0004467542049895</v>
       </c>
-      <c r="I40" t="n">
+      <c r="K40" t="n">
         <v>2.234109126211351e-06</v>
       </c>
-      <c r="J40" t="n">
+      <c r="L40" t="n">
         <v>0.00742246114900285</v>
       </c>
-      <c r="K40" t="n">
+      <c r="M40" t="n">
         <v>0.4920799256630596</v>
       </c>
-      <c r="L40" t="n">
+      <c r="N40" t="n">
         <v>0.0157815920475604</v>
       </c>
-      <c r="M40" t="n">
+      <c r="O40" t="n">
         <v>0.0026940019135316</v>
       </c>
-      <c r="N40" t="n">
+      <c r="P40" t="n">
         <v>0.01957749939099619</v>
       </c>
-      <c r="O40" t="n">
+      <c r="Q40" t="n">
         <v>0.009399130095669301</v>
       </c>
-      <c r="P40" t="n">
+      <c r="R40" t="n">
         <v>0.4500622542716237</v>
       </c>
-      <c r="Q40" t="n">
+      <c r="S40" t="n">
         <v>3.812223019598695e-05</v>
       </c>
-      <c r="R40" t="n">
+      <c r="T40" t="n">
         <v>0.0012595669905566</v>
       </c>
-      <c r="S40" t="n">
+      <c r="U40" t="n">
         <v>4.202432496038501e-05</v>
       </c>
-      <c r="T40" t="n">
+      <c r="V40" t="n">
         <v>0.0016434088612988</v>
       </c>
-      <c r="U40" t="n">
-        <v>0</v>
-      </c>
-      <c r="V40" t="n">
-        <v>1</v>
-      </c>
       <c r="W40" t="n">
         <v>0</v>
       </c>
@@ -6135,10 +6368,10 @@
         <v>0</v>
       </c>
       <c r="Z40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB40" t="n">
         <v>0</v>
@@ -6150,51 +6383,57 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF40" t="n">
         <v>0</v>
       </c>
       <c r="AG40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AH40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI40" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ40" t="n">
         <v>0</v>
       </c>
       <c r="AK40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM40" t="n">
         <v>0.4985432088565234</v>
       </c>
-      <c r="AL40" t="n">
+      <c r="AN40" t="n">
         <v>0.0014567911434765</v>
       </c>
-      <c r="AM40" t="n">
-        <v>1</v>
-      </c>
-      <c r="AN40" t="n">
-        <v>0</v>
-      </c>
       <c r="AO40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AP40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR40" t="n">
         <v>0.5</v>
       </c>
-      <c r="AQ40" t="n">
+      <c r="AS40" t="n">
         <v>0.05560920051769665</v>
       </c>
-      <c r="AR40" t="n">
+      <c r="AT40" t="n">
         <v>0.4443907994823033</v>
       </c>
-      <c r="AS40" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT40" t="n">
+      <c r="AU40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV40" t="n">
         <v>1</v>
       </c>
     </row>
